--- a/_assets/includes/documents/FormatoPrecio.xlsx
+++ b/_assets/includes/documents/FormatoPrecio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.3\wwwroot\TG_PHP\_assets\includes\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alejandro.martinez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A40A838-03A5-4494-A16E-CEA5E996A046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5AE56C-D86C-43E9-90CB-C418423C9D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57A7AD68-8712-49E5-8AAC-8C9DF7ECE3A4}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="119">
   <si>
     <t>precio pemex</t>
   </si>
@@ -587,6 +587,9 @@
   </si>
   <si>
     <t>FLASH BP  PL/907/EXP/ES/2015    2.572</t>
+  </si>
+  <si>
+    <t>CIRCLE K  PL/4956/EXP/ES/2015  2.1 km</t>
   </si>
 </sst>
 </file>
@@ -1352,6 +1355,27 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1376,31 +1400,10 @@
     <xf numFmtId="14" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1737,7 +1740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97394460-1E87-45F2-A434-F65D90B57D24}">
-  <dimension ref="A1:G240"/>
+  <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77" style="10" bestFit="1" customWidth="1"/>
@@ -1751,8 +1754,8 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="90"/>
-      <c r="F1" s="91"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="98"/>
       <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1859,8 +1862,8 @@
     </row>
     <row r="14" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
-      <c r="E14" s="92"/>
-      <c r="F14" s="93"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="100"/>
       <c r="G14" s="35"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2004,8 +2007,8 @@
       <c r="G24" s="41"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E25" s="94"/>
-      <c r="F25" s="95"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="102"/>
       <c r="G25" s="42"/>
     </row>
     <row r="26" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -2123,8 +2126,8 @@
       <c r="A42" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E42" s="96"/>
-      <c r="F42" s="97"/>
+      <c r="E42" s="93"/>
+      <c r="F42" s="94"/>
       <c r="G42" s="64"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2198,9 +2201,9 @@
       <c r="G47" s="56"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E48" s="98"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="100"/>
+      <c r="E48" s="90"/>
+      <c r="F48" s="91"/>
+      <c r="G48" s="92"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="str">
@@ -2239,8 +2242,8 @@
       <c r="A55" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E55" s="96"/>
-      <c r="F55" s="97"/>
+      <c r="E55" s="93"/>
+      <c r="F55" s="94"/>
       <c r="G55" s="64"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2292,9 +2295,9 @@
       <c r="G59" s="56"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E60" s="98"/>
-      <c r="F60" s="99"/>
-      <c r="G60" s="100"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="92"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="str">
@@ -2350,8 +2353,8 @@
       <c r="A68" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E68" s="96"/>
-      <c r="F68" s="97"/>
+      <c r="E68" s="93"/>
+      <c r="F68" s="94"/>
       <c r="G68" s="64"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -2389,9 +2392,9 @@
       <c r="G71" s="56"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E72" s="98"/>
-      <c r="F72" s="99"/>
-      <c r="G72" s="100"/>
+      <c r="E72" s="90"/>
+      <c r="F72" s="91"/>
+      <c r="G72" s="92"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="str">
@@ -2438,8 +2441,8 @@
       <c r="A80" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E80" s="101"/>
-      <c r="F80" s="102"/>
+      <c r="E80" s="103"/>
+      <c r="F80" s="104"/>
       <c r="G80" s="71"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -2569,9 +2572,9 @@
       <c r="G89" s="70"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E90" s="98"/>
-      <c r="F90" s="99"/>
-      <c r="G90" s="100"/>
+      <c r="E90" s="90"/>
+      <c r="F90" s="91"/>
+      <c r="G90" s="92"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="str">
@@ -2622,8 +2625,8 @@
       <c r="A97" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E97" s="88"/>
-      <c r="F97" s="89"/>
+      <c r="E97" s="95"/>
+      <c r="F97" s="96"/>
       <c r="G97" s="71"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -2669,11 +2672,11 @@
       <c r="G100" s="74"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="21" t="s">
-        <v>44</v>
+      <c r="A101" s="15" t="s">
+        <v>118</v>
       </c>
       <c r="B101">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -2684,10 +2687,10 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B102">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C102">
         <v>4</v>
@@ -2698,10 +2701,10 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B103">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="C103">
         <v>4</v>
@@ -2712,10 +2715,10 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B104">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C104">
         <v>4</v>
@@ -2725,11 +2728,11 @@
       <c r="G104" s="74"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="22" t="s">
-        <v>48</v>
+      <c r="A105" s="21" t="s">
+        <v>47</v>
       </c>
       <c r="B105">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C105">
         <v>4</v>
@@ -2739,11 +2742,11 @@
       <c r="G105" s="74"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="21" t="s">
-        <v>49</v>
+      <c r="A106" s="22" t="s">
+        <v>48</v>
       </c>
       <c r="B106">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C106">
         <v>4</v>
@@ -2754,10 +2757,10 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="21" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="B107">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C107">
         <v>4</v>
@@ -2767,103 +2770,103 @@
       <c r="G107" s="74"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="79" t="s">
-        <v>50</v>
+      <c r="A108" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="B108">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C108">
         <v>4</v>
       </c>
       <c r="E108" s="72"/>
-      <c r="F108" s="75"/>
+      <c r="F108" s="73"/>
       <c r="G108" s="74"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E109" s="76"/>
-      <c r="F109" s="77"/>
-      <c r="G109" s="57"/>
+      <c r="A109" s="79" t="s">
+        <v>50</v>
+      </c>
+      <c r="B109">
+        <v>58</v>
+      </c>
+      <c r="C109">
+        <v>4</v>
+      </c>
+      <c r="E109" s="72"/>
+      <c r="F109" s="75"/>
+      <c r="G109" s="74"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="14" t="str">
+      <c r="E110" s="76"/>
+      <c r="F110" s="77"/>
+      <c r="G110" s="57"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="14" t="str">
         <f>A96</f>
         <v>DELICIAS</v>
       </c>
-      <c r="B110">
+      <c r="B111">
         <v>1</v>
       </c>
-      <c r="C110">
+      <c r="C111">
         <v>4</v>
       </c>
-      <c r="E110" s="32"/>
-      <c r="F110" s="33"/>
-      <c r="G110" s="34"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="23"/>
-      <c r="G112" s="49"/>
+      <c r="E111" s="32"/>
+      <c r="F111" s="33"/>
+      <c r="G111" s="34"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E113" s="58"/>
-      <c r="F113" s="59"/>
-      <c r="G113" s="60"/>
-    </row>
-    <row r="114" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E114" s="61"/>
-      <c r="F114" s="62"/>
-      <c r="G114" s="63"/>
-    </row>
-    <row r="115" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A115" s="16" t="s">
+      <c r="A113" s="23"/>
+      <c r="G113" s="49"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E114" s="58"/>
+      <c r="F114" s="59"/>
+      <c r="G114" s="60"/>
+    </row>
+    <row r="115" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E115" s="61"/>
+      <c r="F115" s="62"/>
+      <c r="G115" s="63"/>
+    </row>
+    <row r="116" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A116" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E115" s="32"/>
-      <c r="F115" s="33"/>
-      <c r="G115" s="34"/>
-    </row>
-    <row r="116" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="14" t="s">
+      <c r="E116" s="32"/>
+      <c r="F116" s="33"/>
+      <c r="G116" s="34"/>
+    </row>
+    <row r="117" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E116" s="103"/>
-      <c r="F116" s="104"/>
-      <c r="G116" s="64"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B117">
-        <v>2</v>
-      </c>
-      <c r="C117">
-        <v>3</v>
-      </c>
-      <c r="E117" s="65"/>
-      <c r="F117" s="66"/>
-      <c r="G117" s="67"/>
+      <c r="E117" s="88"/>
+      <c r="F117" s="89"/>
+      <c r="G117" s="64"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B118">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C118">
         <v>3</v>
       </c>
-      <c r="E118" s="68"/>
-      <c r="F118" s="69"/>
-      <c r="G118" s="70"/>
+      <c r="E118" s="65"/>
+      <c r="F118" s="66"/>
+      <c r="G118" s="67"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B119">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="C119">
         <v>3</v>
@@ -2873,71 +2876,71 @@
       <c r="G119" s="70"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E120" s="98"/>
-      <c r="F120" s="99"/>
-      <c r="G120" s="100"/>
+      <c r="A120" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B120">
+        <v>61</v>
+      </c>
+      <c r="C120">
+        <v>3</v>
+      </c>
+      <c r="E120" s="68"/>
+      <c r="F120" s="69"/>
+      <c r="G120" s="70"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="14" t="str">
-        <f>A115</f>
+      <c r="E121" s="90"/>
+      <c r="F121" s="91"/>
+      <c r="G121" s="92"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="14" t="str">
+        <f>A116</f>
         <v>AHUMADA</v>
       </c>
-      <c r="B121">
+      <c r="B122">
         <v>1</v>
       </c>
-      <c r="C121">
+      <c r="C122">
         <v>3</v>
       </c>
-      <c r="E121" s="32"/>
-      <c r="F121" s="33"/>
-      <c r="G121" s="34"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E124" s="50"/>
-      <c r="F124" s="51"/>
-      <c r="G124" s="52"/>
-    </row>
-    <row r="125" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E125" s="53"/>
-      <c r="F125" s="54"/>
-      <c r="G125" s="55"/>
-    </row>
-    <row r="126" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="13" t="s">
+      <c r="E122" s="32"/>
+      <c r="F122" s="33"/>
+      <c r="G122" s="34"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E125" s="50"/>
+      <c r="F125" s="51"/>
+      <c r="G125" s="52"/>
+    </row>
+    <row r="126" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E126" s="53"/>
+      <c r="F126" s="54"/>
+      <c r="G126" s="55"/>
+    </row>
+    <row r="127" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E126" s="32"/>
-      <c r="F126" s="33"/>
-      <c r="G126" s="34"/>
-    </row>
-    <row r="127" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="14" t="s">
+      <c r="E127" s="32"/>
+      <c r="F127" s="33"/>
+      <c r="G127" s="34"/>
+    </row>
+    <row r="128" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E127" s="103"/>
-      <c r="F127" s="104"/>
-      <c r="G127" s="35"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B128">
-        <v>41</v>
-      </c>
-      <c r="C128">
-        <v>2</v>
-      </c>
-      <c r="E128" s="47"/>
-      <c r="F128" s="48"/>
-      <c r="G128" s="56"/>
+      <c r="E128" s="88"/>
+      <c r="F128" s="89"/>
+      <c r="G128" s="35"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B129">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -2948,10 +2951,10 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B130">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -2962,10 +2965,10 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B131">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -2976,10 +2979,10 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B132">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C132">
         <v>2</v>
@@ -2990,10 +2993,10 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B133">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C133">
         <v>2</v>
@@ -3004,10 +3007,10 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B134">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C134">
         <v>2</v>
@@ -3018,10 +3021,10 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B135">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C135">
         <v>2</v>
@@ -3031,71 +3034,71 @@
       <c r="G135" s="56"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E136" s="98"/>
-      <c r="F136" s="99"/>
-      <c r="G136" s="100"/>
+      <c r="A136" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B136">
+        <v>16</v>
+      </c>
+      <c r="C136">
+        <v>2</v>
+      </c>
+      <c r="E136" s="47"/>
+      <c r="F136" s="48"/>
+      <c r="G136" s="56"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="14" t="str">
-        <f>A126</f>
+      <c r="E137" s="90"/>
+      <c r="F137" s="91"/>
+      <c r="G137" s="92"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="14" t="str">
+        <f>A127</f>
         <v>INDEPENDENCIA</v>
       </c>
-      <c r="B137">
+      <c r="B138">
         <v>1</v>
       </c>
-      <c r="C137">
+      <c r="C138">
         <v>2</v>
       </c>
-      <c r="E137" s="32"/>
-      <c r="F137" s="33"/>
-      <c r="G137" s="34"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E140" s="58"/>
-      <c r="F140" s="59"/>
-      <c r="G140" s="60"/>
-    </row>
-    <row r="141" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E141" s="61"/>
-      <c r="F141" s="62"/>
-      <c r="G141" s="63"/>
-    </row>
-    <row r="142" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A142" s="16" t="s">
+      <c r="E138" s="32"/>
+      <c r="F138" s="33"/>
+      <c r="G138" s="34"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E141" s="58"/>
+      <c r="F141" s="59"/>
+      <c r="G141" s="60"/>
+    </row>
+    <row r="142" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E142" s="61"/>
+      <c r="F142" s="62"/>
+      <c r="G142" s="63"/>
+    </row>
+    <row r="143" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A143" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E142" s="32"/>
-      <c r="F142" s="33"/>
-      <c r="G142" s="34"/>
-    </row>
-    <row r="143" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="14" t="s">
+      <c r="E143" s="32"/>
+      <c r="F143" s="33"/>
+      <c r="G143" s="34"/>
+    </row>
+    <row r="144" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E143" s="103"/>
-      <c r="F143" s="104"/>
-      <c r="G143" s="64"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B144">
-        <v>12</v>
-      </c>
-      <c r="C144">
-        <v>5</v>
-      </c>
-      <c r="E144" s="68"/>
-      <c r="F144" s="69"/>
-      <c r="G144" s="70"/>
+      <c r="E144" s="88"/>
+      <c r="F144" s="89"/>
+      <c r="G144" s="64"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B145">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C145">
         <v>5</v>
@@ -3106,10 +3109,10 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B146">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C146">
         <v>5</v>
@@ -3120,10 +3123,10 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B147">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C147">
         <v>5</v>
@@ -3134,10 +3137,10 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B148">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C148">
         <v>5</v>
@@ -3148,10 +3151,10 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="B149">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C149">
         <v>5</v>
@@ -3162,10 +3165,10 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="17" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="B150">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C150">
         <v>5</v>
@@ -3176,10 +3179,10 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B151">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C151">
         <v>5</v>
@@ -3189,71 +3192,71 @@
       <c r="G151" s="70"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E152" s="98"/>
-      <c r="F152" s="99"/>
-      <c r="G152" s="100"/>
+      <c r="A152" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B152">
+        <v>18</v>
+      </c>
+      <c r="C152">
+        <v>5</v>
+      </c>
+      <c r="E152" s="68"/>
+      <c r="F152" s="69"/>
+      <c r="G152" s="70"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="14" t="str">
-        <f>A142</f>
+      <c r="E153" s="90"/>
+      <c r="F153" s="91"/>
+      <c r="G153" s="92"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="14" t="str">
+        <f>A143</f>
         <v>CASTAÑO</v>
       </c>
-      <c r="B153">
+      <c r="B154">
         <v>1</v>
       </c>
-      <c r="C153">
+      <c r="C154">
         <v>5</v>
       </c>
-      <c r="E153" s="32"/>
-      <c r="F153" s="33"/>
-      <c r="G153" s="34"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E156" s="50"/>
-      <c r="F156" s="51"/>
-      <c r="G156" s="52"/>
-    </row>
-    <row r="157" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E157" s="53"/>
-      <c r="F157" s="54"/>
-      <c r="G157" s="55"/>
-    </row>
-    <row r="158" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A158" s="16" t="s">
+      <c r="E154" s="32"/>
+      <c r="F154" s="33"/>
+      <c r="G154" s="34"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E157" s="50"/>
+      <c r="F157" s="51"/>
+      <c r="G157" s="52"/>
+    </row>
+    <row r="158" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E158" s="53"/>
+      <c r="F158" s="54"/>
+      <c r="G158" s="55"/>
+    </row>
+    <row r="159" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A159" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E158" s="32"/>
-      <c r="F158" s="33"/>
-      <c r="G158" s="34"/>
-    </row>
-    <row r="159" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="14" t="s">
+      <c r="E159" s="32"/>
+      <c r="F159" s="33"/>
+      <c r="G159" s="34"/>
+    </row>
+    <row r="160" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E159" s="96"/>
-      <c r="F159" s="97"/>
-      <c r="G159" s="64"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="B160">
-        <v>65</v>
-      </c>
-      <c r="C160">
-        <v>11</v>
-      </c>
-      <c r="E160" s="47"/>
-      <c r="F160" s="48"/>
-      <c r="G160" s="56"/>
+      <c r="E160" s="93"/>
+      <c r="F160" s="94"/>
+      <c r="G160" s="64"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="B161">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C161">
         <v>11</v>
@@ -3264,10 +3267,10 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B162">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C162">
         <v>11</v>
@@ -3278,10 +3281,10 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B163">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C163">
         <v>11</v>
@@ -3292,10 +3295,10 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B164">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C164">
         <v>11</v>
@@ -3305,83 +3308,83 @@
       <c r="G164" s="56"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="17"/>
+      <c r="A165" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B165">
+        <v>68</v>
+      </c>
+      <c r="C165">
+        <v>11</v>
+      </c>
       <c r="E165" s="47"/>
       <c r="F165" s="48"/>
       <c r="G165" s="56"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E166" s="98"/>
-      <c r="F166" s="99"/>
-      <c r="G166" s="100"/>
-    </row>
-    <row r="167" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A167" s="80" t="str">
-        <f>A158</f>
+      <c r="A166" s="17"/>
+      <c r="E166" s="47"/>
+      <c r="F166" s="48"/>
+      <c r="G166" s="56"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E167" s="90"/>
+      <c r="F167" s="91"/>
+      <c r="G167" s="92"/>
+    </row>
+    <row r="168" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A168" s="80" t="str">
+        <f>A159</f>
         <v>San Rafael</v>
       </c>
-      <c r="B167">
+      <c r="B168">
         <v>1</v>
       </c>
-      <c r="C167">
+      <c r="C168">
         <v>11</v>
       </c>
-      <c r="E167" s="43"/>
-      <c r="F167" s="44"/>
-      <c r="G167" s="45"/>
-    </row>
-    <row r="168" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A168" s="80"/>
-      <c r="E168" s="78"/>
-      <c r="F168" s="78"/>
-      <c r="G168" s="78"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E170" s="50"/>
-      <c r="F170" s="51"/>
-      <c r="G170" s="52"/>
-    </row>
-    <row r="171" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E171" s="53"/>
-      <c r="F171" s="54"/>
-      <c r="G171" s="55"/>
-    </row>
-    <row r="172" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A172" s="16" t="s">
+      <c r="E168" s="43"/>
+      <c r="F168" s="44"/>
+      <c r="G168" s="45"/>
+    </row>
+    <row r="169" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A169" s="80"/>
+      <c r="E169" s="78"/>
+      <c r="F169" s="78"/>
+      <c r="G169" s="78"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E171" s="50"/>
+      <c r="F171" s="51"/>
+      <c r="G171" s="52"/>
+    </row>
+    <row r="172" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E172" s="53"/>
+      <c r="F172" s="54"/>
+      <c r="G172" s="55"/>
+    </row>
+    <row r="173" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A173" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E172" s="32"/>
-      <c r="F172" s="33"/>
-      <c r="G172" s="34"/>
-    </row>
-    <row r="173" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="14" t="s">
+      <c r="E173" s="32"/>
+      <c r="F173" s="33"/>
+      <c r="G173" s="34"/>
+    </row>
+    <row r="174" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E173" s="96"/>
-      <c r="F173" s="97"/>
-      <c r="G173" s="64"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A174" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B174">
-        <v>81</v>
-      </c>
-      <c r="C174">
-        <v>12</v>
-      </c>
-      <c r="E174" s="47"/>
-      <c r="F174" s="48"/>
-      <c r="G174" s="56"/>
+      <c r="E174" s="93"/>
+      <c r="F174" s="94"/>
+      <c r="G174" s="64"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B175">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C175">
         <v>12</v>
@@ -3392,10 +3395,10 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="15" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B176">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C176">
         <v>12</v>
@@ -3406,10 +3409,10 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="15" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="B177">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C177">
         <v>12</v>
@@ -3419,77 +3422,77 @@
       <c r="G177" s="56"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E178" s="98"/>
-      <c r="F178" s="99"/>
-      <c r="G178" s="100"/>
-    </row>
-    <row r="179" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A179" s="80" t="str">
-        <f>A172</f>
+      <c r="A178" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B178">
+        <v>72</v>
+      </c>
+      <c r="C178">
+        <v>12</v>
+      </c>
+      <c r="E178" s="47"/>
+      <c r="F178" s="48"/>
+      <c r="G178" s="56"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E179" s="90"/>
+      <c r="F179" s="91"/>
+      <c r="G179" s="92"/>
+    </row>
+    <row r="180" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A180" s="80" t="str">
+        <f>A173</f>
         <v>Puertecito</v>
       </c>
-      <c r="B179">
+      <c r="B180">
         <v>1</v>
       </c>
-      <c r="C179">
+      <c r="C180">
         <v>12</v>
       </c>
-      <c r="E179" s="43"/>
-      <c r="F179" s="44"/>
-      <c r="G179" s="45"/>
-    </row>
-    <row r="180" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A180" s="80"/>
-      <c r="E180" s="78"/>
-      <c r="F180" s="78"/>
-      <c r="G180" s="78"/>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E182" s="50"/>
-      <c r="F182" s="51"/>
-      <c r="G182" s="52"/>
-    </row>
-    <row r="183" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E183" s="53"/>
-      <c r="F183" s="54"/>
-      <c r="G183" s="55"/>
-    </row>
-    <row r="184" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A184" s="16" t="s">
+      <c r="E180" s="43"/>
+      <c r="F180" s="44"/>
+      <c r="G180" s="45"/>
+    </row>
+    <row r="181" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A181" s="80"/>
+      <c r="E181" s="78"/>
+      <c r="F181" s="78"/>
+      <c r="G181" s="78"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E183" s="50"/>
+      <c r="F183" s="51"/>
+      <c r="G183" s="52"/>
+    </row>
+    <row r="184" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E184" s="53"/>
+      <c r="F184" s="54"/>
+      <c r="G184" s="55"/>
+    </row>
+    <row r="185" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A185" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E184" s="32"/>
-      <c r="F184" s="33"/>
-      <c r="G184" s="34"/>
-    </row>
-    <row r="185" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="14" t="s">
+      <c r="E185" s="32"/>
+      <c r="F185" s="33"/>
+      <c r="G185" s="34"/>
+    </row>
+    <row r="186" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E185" s="96"/>
-      <c r="F185" s="97"/>
-      <c r="G185" s="64"/>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B186">
-        <v>73</v>
-      </c>
-      <c r="C186">
-        <v>13</v>
-      </c>
-      <c r="E186" s="47"/>
-      <c r="F186" s="48"/>
-      <c r="G186" s="56"/>
+      <c r="E186" s="93"/>
+      <c r="F186" s="94"/>
+      <c r="G186" s="64"/>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B187">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C187">
         <v>13</v>
@@ -3500,10 +3503,10 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B188">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C188">
         <v>13</v>
@@ -3514,10 +3517,10 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="15" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="B189">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C189">
         <v>13</v>
@@ -3528,10 +3531,10 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="15" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="B190">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C190">
         <v>13</v>
@@ -3541,77 +3544,77 @@
       <c r="G190" s="56"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E191" s="98"/>
-      <c r="F191" s="99"/>
-      <c r="G191" s="100"/>
-    </row>
-    <row r="192" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A192" s="80" t="str">
-        <f>A184</f>
+      <c r="A191" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B191">
+        <v>75</v>
+      </c>
+      <c r="C191">
+        <v>13</v>
+      </c>
+      <c r="E191" s="47"/>
+      <c r="F191" s="48"/>
+      <c r="G191" s="56"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E192" s="90"/>
+      <c r="F192" s="91"/>
+      <c r="G192" s="92"/>
+    </row>
+    <row r="193" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A193" s="80" t="str">
+        <f>A185</f>
         <v>Colosio</v>
       </c>
-      <c r="B192">
+      <c r="B193">
         <v>1</v>
       </c>
-      <c r="C192">
+      <c r="C193">
         <v>13</v>
       </c>
-      <c r="E192" s="43"/>
-      <c r="F192" s="44"/>
-      <c r="G192" s="45"/>
-    </row>
-    <row r="193" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A193"/>
-      <c r="E193"/>
-      <c r="F193"/>
-      <c r="G193"/>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E195" s="50"/>
-      <c r="F195" s="51"/>
-      <c r="G195" s="52"/>
-    </row>
-    <row r="196" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E196" s="53"/>
-      <c r="F196" s="54"/>
-      <c r="G196" s="55"/>
-    </row>
-    <row r="197" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A197" s="16" t="s">
+      <c r="E193" s="43"/>
+      <c r="F193" s="44"/>
+      <c r="G193" s="45"/>
+    </row>
+    <row r="194" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A194"/>
+      <c r="E194"/>
+      <c r="F194"/>
+      <c r="G194"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E196" s="50"/>
+      <c r="F196" s="51"/>
+      <c r="G196" s="52"/>
+    </row>
+    <row r="197" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E197" s="53"/>
+      <c r="F197" s="54"/>
+      <c r="G197" s="55"/>
+    </row>
+    <row r="198" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A198" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E197" s="32"/>
-      <c r="F197" s="33"/>
-      <c r="G197" s="34"/>
-    </row>
-    <row r="198" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="14" t="s">
+      <c r="E198" s="32"/>
+      <c r="F198" s="33"/>
+      <c r="G198" s="34"/>
+    </row>
+    <row r="199" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E198" s="96"/>
-      <c r="F198" s="97"/>
-      <c r="G198" s="64"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A199" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B199">
-        <v>76</v>
-      </c>
-      <c r="C199">
-        <v>14</v>
-      </c>
-      <c r="E199" s="47"/>
-      <c r="F199" s="48"/>
-      <c r="G199" s="56"/>
+      <c r="E199" s="93"/>
+      <c r="F199" s="94"/>
+      <c r="G199" s="64"/>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B200">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C200">
         <v>14</v>
@@ -3622,10 +3625,10 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B201">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C201">
         <v>14</v>
@@ -3636,10 +3639,10 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="15" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B202">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C202">
         <v>14</v>
@@ -3649,71 +3652,71 @@
       <c r="G202" s="56"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E203" s="98"/>
-      <c r="F203" s="99"/>
-      <c r="G203" s="100"/>
-    </row>
-    <row r="204" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A204" s="80" t="str">
-        <f>A197</f>
+      <c r="A203" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B203">
+        <v>79</v>
+      </c>
+      <c r="C203">
+        <v>14</v>
+      </c>
+      <c r="E203" s="47"/>
+      <c r="F203" s="48"/>
+      <c r="G203" s="56"/>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E204" s="90"/>
+      <c r="F204" s="91"/>
+      <c r="G204" s="92"/>
+    </row>
+    <row r="205" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A205" s="80" t="str">
+        <f>A198</f>
         <v xml:space="preserve">Jesus Maria </v>
       </c>
-      <c r="B204">
+      <c r="B205">
         <v>1</v>
       </c>
-      <c r="C204">
+      <c r="C205">
         <v>14</v>
       </c>
-      <c r="E204" s="43"/>
-      <c r="F204" s="44"/>
-      <c r="G204" s="45"/>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E207" s="50"/>
-      <c r="F207" s="51"/>
-      <c r="G207" s="52"/>
-    </row>
-    <row r="208" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E208" s="53"/>
-      <c r="F208" s="54"/>
-      <c r="G208" s="55"/>
-    </row>
-    <row r="209" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A209" s="16" t="s">
+      <c r="E205" s="43"/>
+      <c r="F205" s="44"/>
+      <c r="G205" s="45"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E208" s="50"/>
+      <c r="F208" s="51"/>
+      <c r="G208" s="52"/>
+    </row>
+    <row r="209" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E209" s="53"/>
+      <c r="F209" s="54"/>
+      <c r="G209" s="55"/>
+    </row>
+    <row r="210" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A210" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="E209" s="32"/>
-      <c r="F209" s="33"/>
-      <c r="G209" s="34"/>
-    </row>
-    <row r="210" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="14" t="s">
+      <c r="E210" s="32"/>
+      <c r="F210" s="33"/>
+      <c r="G210" s="34"/>
+    </row>
+    <row r="211" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E210" s="96"/>
-      <c r="F210" s="97"/>
-      <c r="G210" s="64"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A211" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B211">
-        <v>87</v>
-      </c>
-      <c r="C211">
-        <v>16</v>
-      </c>
-      <c r="E211" s="47"/>
-      <c r="F211" s="48"/>
-      <c r="G211" s="56"/>
+      <c r="E211" s="93"/>
+      <c r="F211" s="94"/>
+      <c r="G211" s="64"/>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B212">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C212">
         <v>16</v>
@@ -3724,10 +3727,10 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B213">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C213">
         <v>16</v>
@@ -3738,10 +3741,10 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B214">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C214">
         <v>16</v>
@@ -3751,71 +3754,71 @@
       <c r="G214" s="56"/>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E215" s="98"/>
-      <c r="F215" s="99"/>
-      <c r="G215" s="100"/>
-    </row>
-    <row r="216" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A216" s="80" t="str">
-        <f>A209</f>
+      <c r="A215" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B215">
+        <v>90</v>
+      </c>
+      <c r="C215">
+        <v>16</v>
+      </c>
+      <c r="E215" s="47"/>
+      <c r="F215" s="48"/>
+      <c r="G215" s="56"/>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E216" s="90"/>
+      <c r="F216" s="91"/>
+      <c r="G216" s="92"/>
+    </row>
+    <row r="217" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A217" s="80" t="str">
+        <f>A210</f>
         <v xml:space="preserve">Gabriela Mistral </v>
       </c>
-      <c r="B216">
+      <c r="B217">
         <v>1</v>
       </c>
-      <c r="C216">
+      <c r="C217">
         <v>16</v>
       </c>
-      <c r="E216" s="43"/>
-      <c r="F216" s="44"/>
-      <c r="G216" s="45"/>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E219" s="50"/>
-      <c r="F219" s="51"/>
-      <c r="G219" s="52"/>
-    </row>
-    <row r="220" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E220" s="53"/>
-      <c r="F220" s="54"/>
-      <c r="G220" s="55"/>
-    </row>
-    <row r="221" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A221" s="16" t="s">
+      <c r="E217" s="43"/>
+      <c r="F217" s="44"/>
+      <c r="G217" s="45"/>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E220" s="50"/>
+      <c r="F220" s="51"/>
+      <c r="G220" s="52"/>
+    </row>
+    <row r="221" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E221" s="53"/>
+      <c r="F221" s="54"/>
+      <c r="G221" s="55"/>
+    </row>
+    <row r="222" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A222" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E221" s="32"/>
-      <c r="F221" s="33"/>
-      <c r="G221" s="34"/>
-    </row>
-    <row r="222" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="14" t="s">
+      <c r="E222" s="32"/>
+      <c r="F222" s="33"/>
+      <c r="G222" s="34"/>
+    </row>
+    <row r="223" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E222" s="96"/>
-      <c r="F222" s="97"/>
-      <c r="G222" s="64"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A223" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B223">
-        <v>11</v>
-      </c>
-      <c r="C223">
-        <v>7</v>
-      </c>
-      <c r="E223" s="47"/>
-      <c r="F223" s="48"/>
-      <c r="G223" s="56"/>
+      <c r="E223" s="93"/>
+      <c r="F223" s="94"/>
+      <c r="G223" s="64"/>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="17" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="B224">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="C224">
         <v>7</v>
@@ -3826,10 +3829,10 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B225">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C225">
         <v>7</v>
@@ -3839,78 +3842,78 @@
       <c r="G225" s="56"/>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A226" s="17"/>
+      <c r="A226" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B226">
+        <v>51</v>
+      </c>
+      <c r="C226">
+        <v>7</v>
+      </c>
       <c r="E226" s="47"/>
       <c r="F226" s="48"/>
       <c r="G226" s="56"/>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E227" s="98"/>
-      <c r="F227" s="99"/>
-      <c r="G227" s="100"/>
+      <c r="A227" s="17"/>
+      <c r="E227" s="47"/>
+      <c r="F227" s="48"/>
+      <c r="G227" s="56"/>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A228" s="14" t="str">
-        <f>A221</f>
+      <c r="E228" s="90"/>
+      <c r="F228" s="91"/>
+      <c r="G228" s="92"/>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="14" t="str">
+        <f>A222</f>
         <v xml:space="preserve">PICACHOS </v>
       </c>
-      <c r="B228">
+      <c r="B229">
         <v>1</v>
       </c>
-      <c r="C228">
+      <c r="C229">
         <v>7</v>
       </c>
-      <c r="E228" s="32"/>
-      <c r="F228" s="33"/>
-      <c r="G228" s="34"/>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A231" s="14"/>
-      <c r="E231" s="50"/>
-      <c r="F231" s="51"/>
-      <c r="G231" s="52"/>
-    </row>
-    <row r="232" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E232" s="53"/>
-      <c r="F232" s="54"/>
-      <c r="G232" s="55"/>
-    </row>
-    <row r="233" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A233" s="16" t="s">
+      <c r="E229" s="32"/>
+      <c r="F229" s="33"/>
+      <c r="G229" s="34"/>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="14"/>
+      <c r="E232" s="50"/>
+      <c r="F232" s="51"/>
+      <c r="G232" s="52"/>
+    </row>
+    <row r="233" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E233" s="53"/>
+      <c r="F233" s="54"/>
+      <c r="G233" s="55"/>
+    </row>
+    <row r="234" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A234" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E233" s="32"/>
-      <c r="F233" s="33"/>
-      <c r="G233" s="34"/>
-    </row>
-    <row r="234" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="14" t="s">
+      <c r="E234" s="32"/>
+      <c r="F234" s="33"/>
+      <c r="G234" s="34"/>
+    </row>
+    <row r="235" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E234" s="103"/>
-      <c r="F234" s="104"/>
-      <c r="G234" s="64"/>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A235" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B235">
-        <v>19</v>
-      </c>
-      <c r="C235">
-        <v>9</v>
-      </c>
-      <c r="E235" s="47"/>
-      <c r="F235" s="48"/>
-      <c r="G235" s="56"/>
+      <c r="E235" s="88"/>
+      <c r="F235" s="89"/>
+      <c r="G235" s="64"/>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B236">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C236">
         <v>9</v>
@@ -3920,7 +3923,15 @@
       <c r="G236" s="56"/>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A237" s="17"/>
+      <c r="A237" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B237">
+        <v>17</v>
+      </c>
+      <c r="C237">
+        <v>9</v>
+      </c>
       <c r="E237" s="47"/>
       <c r="F237" s="48"/>
       <c r="G237" s="56"/>
@@ -3932,47 +3943,33 @@
       <c r="G238" s="56"/>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E239" s="98"/>
-      <c r="F239" s="99"/>
-      <c r="G239" s="100"/>
+      <c r="A239" s="17"/>
+      <c r="E239" s="47"/>
+      <c r="F239" s="48"/>
+      <c r="G239" s="56"/>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A240" s="14" t="str">
-        <f>A233</f>
+      <c r="E240" s="90"/>
+      <c r="F240" s="91"/>
+      <c r="G240" s="92"/>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="14" t="str">
+        <f>A234</f>
         <v>VENTANAS</v>
       </c>
-      <c r="B240">
+      <c r="B241">
         <v>1</v>
       </c>
-      <c r="C240">
+      <c r="C241">
         <v>9</v>
       </c>
-      <c r="E240" s="32"/>
-      <c r="F240" s="33"/>
-      <c r="G240" s="34"/>
+      <c r="E241" s="32"/>
+      <c r="F241" s="33"/>
+      <c r="G241" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="E234:F234"/>
-    <mergeCell ref="E239:G239"/>
-    <mergeCell ref="E198:F198"/>
-    <mergeCell ref="E203:G203"/>
-    <mergeCell ref="E210:F210"/>
-    <mergeCell ref="E215:G215"/>
-    <mergeCell ref="E222:F222"/>
-    <mergeCell ref="E227:G227"/>
-    <mergeCell ref="E191:G191"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="E120:G120"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="E136:G136"/>
-    <mergeCell ref="E143:F143"/>
-    <mergeCell ref="E152:G152"/>
-    <mergeCell ref="E159:F159"/>
-    <mergeCell ref="E166:G166"/>
-    <mergeCell ref="E173:F173"/>
-    <mergeCell ref="E178:G178"/>
-    <mergeCell ref="E185:F185"/>
     <mergeCell ref="E97:F97"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="E14:F14"/>
@@ -3985,6 +3982,26 @@
     <mergeCell ref="E72:G72"/>
     <mergeCell ref="E80:F80"/>
     <mergeCell ref="E90:G90"/>
+    <mergeCell ref="E192:G192"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="E137:G137"/>
+    <mergeCell ref="E144:F144"/>
+    <mergeCell ref="E153:G153"/>
+    <mergeCell ref="E160:F160"/>
+    <mergeCell ref="E167:G167"/>
+    <mergeCell ref="E174:F174"/>
+    <mergeCell ref="E179:G179"/>
+    <mergeCell ref="E186:F186"/>
+    <mergeCell ref="E235:F235"/>
+    <mergeCell ref="E240:G240"/>
+    <mergeCell ref="E199:F199"/>
+    <mergeCell ref="E204:G204"/>
+    <mergeCell ref="E211:F211"/>
+    <mergeCell ref="E216:G216"/>
+    <mergeCell ref="E223:F223"/>
+    <mergeCell ref="E228:G228"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/_assets/includes/documents/FormatoPrecio.xlsx
+++ b/_assets/includes/documents/FormatoPrecio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alejandro.martinez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5AE56C-D86C-43E9-90CB-C418423C9D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0750B068-7B15-44D8-A1B9-897F36CF479A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57A7AD68-8712-49E5-8AAC-8C9DF7ECE3A4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{57A7AD68-8712-49E5-8AAC-8C9DF7ECE3A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="120">
   <si>
     <t>precio pemex</t>
   </si>
@@ -590,6 +590,9 @@
   </si>
   <si>
     <t>CIRCLE K  PL/4956/EXP/ES/2015  2.1 km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVICIO HERNÁNDEZ PL/8708/EXP/ES/2015  1.8 km </t>
   </si>
 </sst>
 </file>
@@ -849,7 +852,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1165,37 +1168,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -1210,7 +1182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1301,9 +1273,6 @@
     <xf numFmtId="164" fontId="21" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="21" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="19" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="19" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="19" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1319,12 +1288,6 @@
     <xf numFmtId="0" fontId="23" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="22" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="20" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="12" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1346,15 +1309,10 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="22" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1376,34 +1334,28 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1740,22 +1692,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97394460-1E87-45F2-A434-F65D90B57D24}">
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G242"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" style="46" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" style="46" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" style="46" customWidth="1"/>
+    <col min="5" max="7" width="19" style="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="97"/>
-      <c r="F1" s="98"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84"/>
       <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1862,8 +1812,8 @@
     </row>
     <row r="14" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="100"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="86"/>
       <c r="G14" s="35"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2007,9 +1957,9 @@
       <c r="G24" s="41"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E25" s="101"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="42"/>
+      <c r="E25" s="78"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="80"/>
     </row>
     <row r="26" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
@@ -2084,7 +2034,7 @@
       <c r="G34" s="34"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="87" t="s">
+      <c r="A35" s="74" t="s">
         <v>102</v>
       </c>
       <c r="E35" s="32"/>
@@ -2095,9 +2045,9 @@
       <c r="A36" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="43"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="45"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="44"/>
     </row>
     <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="E37" s="10"/>
@@ -2105,14 +2055,14 @@
       <c r="G37" s="10"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E39" s="50"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="52"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="51"/>
     </row>
     <row r="40" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E40" s="53"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="55"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="54"/>
     </row>
     <row r="41" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A41" s="16" t="s">
@@ -2126,9 +2076,9 @@
       <c r="A42" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E42" s="93"/>
-      <c r="F42" s="94"/>
-      <c r="G42" s="64"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="82"/>
+      <c r="G42" s="57"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
@@ -2140,9 +2090,9 @@
       <c r="C43">
         <v>8</v>
       </c>
-      <c r="E43" s="47"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="56"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="55"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
@@ -2154,9 +2104,9 @@
       <c r="C44">
         <v>8</v>
       </c>
-      <c r="E44" s="47"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="56"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="55"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
@@ -2168,9 +2118,9 @@
       <c r="C45">
         <v>8</v>
       </c>
-      <c r="E45" s="47"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="56"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="55"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
@@ -2182,9 +2132,9 @@
       <c r="C46">
         <v>8</v>
       </c>
-      <c r="E46" s="47"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="56"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="55"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="24" t="s">
@@ -2196,14 +2146,14 @@
       <c r="C47">
         <v>8</v>
       </c>
-      <c r="E47" s="47"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="56"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="55"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E48" s="90"/>
-      <c r="F48" s="91"/>
-      <c r="G48" s="92"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="80"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="str">
@@ -2216,19 +2166,19 @@
       <c r="C49">
         <v>8</v>
       </c>
-      <c r="E49" s="32"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="34"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="44"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E52" s="50"/>
-      <c r="F52" s="51"/>
-      <c r="G52" s="52"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="51"/>
     </row>
     <row r="53" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E53" s="53"/>
-      <c r="F53" s="54"/>
-      <c r="G53" s="55"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="53"/>
+      <c r="G53" s="54"/>
     </row>
     <row r="54" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A54" s="16" t="s">
@@ -2242,9 +2192,9 @@
       <c r="A55" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E55" s="93"/>
-      <c r="F55" s="94"/>
-      <c r="G55" s="64"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="57"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="17" t="s">
@@ -2256,9 +2206,9 @@
       <c r="C56">
         <v>10</v>
       </c>
-      <c r="E56" s="47"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="56"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="75"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="24" t="s">
@@ -2270,9 +2220,9 @@
       <c r="C57">
         <v>10</v>
       </c>
-      <c r="E57" s="47"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="56"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="55"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
@@ -2284,20 +2234,20 @@
       <c r="C58">
         <v>10</v>
       </c>
-      <c r="E58" s="47"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="56"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="55"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="17"/>
-      <c r="E59" s="47"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="56"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="47"/>
+      <c r="G59" s="55"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E60" s="90"/>
-      <c r="F60" s="91"/>
-      <c r="G60" s="92"/>
+      <c r="E60" s="78"/>
+      <c r="F60" s="79"/>
+      <c r="G60" s="80"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="str">
@@ -2315,9 +2265,9 @@
       <c r="G61" s="34"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E62" s="43"/>
-      <c r="F62" s="44"/>
-      <c r="G62" s="45"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="43"/>
+      <c r="G62" s="44"/>
     </row>
     <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A63"/>
@@ -2332,14 +2282,14 @@
       <c r="G64"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E65" s="50"/>
-      <c r="F65" s="51"/>
-      <c r="G65" s="52"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="51"/>
     </row>
     <row r="66" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E66" s="53"/>
-      <c r="F66" s="54"/>
-      <c r="G66" s="55"/>
+      <c r="E66" s="52"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="54"/>
     </row>
     <row r="67" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A67" s="16" t="s">
@@ -2353,9 +2303,9 @@
       <c r="A68" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E68" s="93"/>
-      <c r="F68" s="94"/>
-      <c r="G68" s="64"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="57"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
@@ -2367,9 +2317,9 @@
       <c r="C69">
         <v>15</v>
       </c>
-      <c r="E69" s="47"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="56"/>
+      <c r="E69" s="46"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="55"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="24" t="s">
@@ -2381,20 +2331,20 @@
       <c r="C70">
         <v>15</v>
       </c>
-      <c r="E70" s="47"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="56"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="55"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="24"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="56"/>
+      <c r="E71" s="46"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="55"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E72" s="90"/>
-      <c r="F72" s="91"/>
-      <c r="G72" s="92"/>
+      <c r="E72" s="78"/>
+      <c r="F72" s="79"/>
+      <c r="G72" s="80"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="str">
@@ -2412,22 +2362,22 @@
       <c r="G73" s="34"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E74" s="43"/>
-      <c r="F74" s="44"/>
-      <c r="G74" s="45"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="43"/>
+      <c r="G74" s="44"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E76" s="49"/>
+      <c r="E76" s="48"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E77" s="58"/>
-      <c r="F77" s="59"/>
-      <c r="G77" s="60"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="50"/>
+      <c r="G77" s="51"/>
     </row>
     <row r="78" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E78" s="61"/>
-      <c r="F78" s="62"/>
-      <c r="G78" s="63"/>
+      <c r="E78" s="52"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="54"/>
     </row>
     <row r="79" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A79" s="16" t="s">
@@ -2441,9 +2391,9 @@
       <c r="A80" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E80" s="103"/>
-      <c r="F80" s="104"/>
-      <c r="G80" s="71"/>
+      <c r="E80" s="87"/>
+      <c r="F80" s="88"/>
+      <c r="G80" s="64"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
@@ -2455,9 +2405,9 @@
       <c r="C81">
         <v>6</v>
       </c>
-      <c r="E81" s="68"/>
-      <c r="F81" s="69"/>
-      <c r="G81" s="70"/>
+      <c r="E81" s="61"/>
+      <c r="F81" s="62"/>
+      <c r="G81" s="63"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="17" t="s">
@@ -2469,9 +2419,9 @@
       <c r="C82">
         <v>6</v>
       </c>
-      <c r="E82" s="68"/>
-      <c r="F82" s="69"/>
-      <c r="G82" s="70"/>
+      <c r="E82" s="61"/>
+      <c r="F82" s="62"/>
+      <c r="G82" s="63"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
@@ -2483,9 +2433,9 @@
       <c r="C83">
         <v>6</v>
       </c>
-      <c r="E83" s="68"/>
-      <c r="F83" s="69"/>
-      <c r="G83" s="70"/>
+      <c r="E83" s="61"/>
+      <c r="F83" s="62"/>
+      <c r="G83" s="63"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="s">
@@ -2497,9 +2447,9 @@
       <c r="C84">
         <v>6</v>
       </c>
-      <c r="E84" s="68"/>
-      <c r="F84" s="69"/>
-      <c r="G84" s="70"/>
+      <c r="E84" s="61"/>
+      <c r="F84" s="62"/>
+      <c r="G84" s="63"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
@@ -2511,9 +2461,9 @@
       <c r="C85">
         <v>6</v>
       </c>
-      <c r="E85" s="68"/>
-      <c r="F85" s="69"/>
-      <c r="G85" s="70"/>
+      <c r="E85" s="61"/>
+      <c r="F85" s="62"/>
+      <c r="G85" s="63"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="s">
@@ -2525,9 +2475,9 @@
       <c r="C86">
         <v>6</v>
       </c>
-      <c r="E86" s="68"/>
-      <c r="F86" s="69"/>
-      <c r="G86" s="70"/>
+      <c r="E86" s="61"/>
+      <c r="F86" s="62"/>
+      <c r="G86" s="63"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
@@ -2539,9 +2489,9 @@
       <c r="C87">
         <v>6</v>
       </c>
-      <c r="E87" s="68"/>
-      <c r="F87" s="69"/>
-      <c r="G87" s="70"/>
+      <c r="E87" s="61"/>
+      <c r="F87" s="62"/>
+      <c r="G87" s="63"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
@@ -2553,1427 +2503,1459 @@
       <c r="C88">
         <v>6</v>
       </c>
-      <c r="E88" s="68"/>
-      <c r="F88" s="69"/>
-      <c r="G88" s="70"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E88" s="61"/>
+      <c r="F88" s="62"/>
+      <c r="G88" s="63"/>
+    </row>
+    <row r="89" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="B89" s="10">
+        <v>92</v>
+      </c>
+      <c r="C89" s="10">
+        <v>6</v>
+      </c>
+      <c r="E89" s="61"/>
+      <c r="F89" s="62"/>
+      <c r="G89" s="63"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B89">
+      <c r="B90">
         <v>22</v>
       </c>
-      <c r="C89">
+      <c r="C90">
         <v>6</v>
       </c>
-      <c r="E89" s="68"/>
-      <c r="F89" s="69"/>
-      <c r="G89" s="70"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E90" s="90"/>
-      <c r="F90" s="91"/>
-      <c r="G90" s="92"/>
+      <c r="E90" s="61"/>
+      <c r="F90" s="62"/>
+      <c r="G90" s="63"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="14" t="str">
+      <c r="E91" s="78"/>
+      <c r="F91" s="79"/>
+      <c r="G91" s="80"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="14" t="str">
         <f>A79</f>
         <v>P A R R A L</v>
       </c>
-      <c r="B91">
+      <c r="B92">
         <v>1</v>
       </c>
-      <c r="C91">
+      <c r="C92">
         <v>6</v>
       </c>
-      <c r="E91" s="32"/>
-      <c r="F91" s="33"/>
-      <c r="G91" s="34"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="18"/>
-      <c r="E92" s="49"/>
-      <c r="F92" s="49"/>
-      <c r="G92" s="49"/>
+      <c r="E92" s="42"/>
+      <c r="F92" s="43"/>
+      <c r="G92" s="44"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="19"/>
-      <c r="E93" s="49"/>
-      <c r="F93" s="49"/>
-      <c r="G93" s="49"/>
+      <c r="A93" s="18"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="48"/>
+      <c r="G93" s="48"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E94" s="81"/>
-      <c r="F94" s="82"/>
-      <c r="G94" s="83"/>
-    </row>
-    <row r="95" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E95" s="84"/>
-      <c r="F95" s="85"/>
-      <c r="G95" s="86"/>
-    </row>
-    <row r="96" spans="1:7" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A96" s="20" t="s">
+      <c r="A94" s="19"/>
+      <c r="E94" s="48"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="48"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E95" s="49"/>
+      <c r="F95" s="50"/>
+      <c r="G95" s="51"/>
+    </row>
+    <row r="96" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E96" s="52"/>
+      <c r="F96" s="53"/>
+      <c r="G96" s="54"/>
+    </row>
+    <row r="97" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A97" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E96" s="32"/>
-      <c r="F96" s="33"/>
-      <c r="G96" s="34"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="14" t="s">
+      <c r="E97" s="32"/>
+      <c r="F97" s="33"/>
+      <c r="G97" s="34"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E97" s="95"/>
-      <c r="F97" s="96"/>
-      <c r="G97" s="71"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B98">
-        <v>18</v>
-      </c>
-      <c r="C98">
-        <v>4</v>
-      </c>
-      <c r="E98" s="72"/>
-      <c r="F98" s="73"/>
-      <c r="G98" s="74"/>
+      <c r="E98" s="89"/>
+      <c r="F98" s="90"/>
+      <c r="G98" s="64"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B99">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C99">
         <v>4</v>
       </c>
-      <c r="E99" s="72"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="74"/>
+      <c r="E99" s="65"/>
+      <c r="F99" s="66"/>
+      <c r="G99" s="67"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="15" t="s">
-        <v>43</v>
+      <c r="A100" s="21" t="s">
+        <v>42</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C100">
         <v>4</v>
       </c>
-      <c r="E100" s="72"/>
-      <c r="F100" s="73"/>
-      <c r="G100" s="74"/>
+      <c r="E100" s="65"/>
+      <c r="F100" s="66"/>
+      <c r="G100" s="67"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="15" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="B101">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="C101">
         <v>4</v>
       </c>
-      <c r="E101" s="72"/>
-      <c r="F101" s="73"/>
-      <c r="G101" s="74"/>
+      <c r="E101" s="65"/>
+      <c r="F101" s="66"/>
+      <c r="G101" s="67"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="21" t="s">
-        <v>44</v>
+      <c r="A102" s="15" t="s">
+        <v>118</v>
       </c>
       <c r="B102">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="C102">
         <v>4</v>
       </c>
-      <c r="E102" s="72"/>
-      <c r="F102" s="73"/>
-      <c r="G102" s="74"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="66"/>
+      <c r="G102" s="67"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B103">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C103">
         <v>4</v>
       </c>
-      <c r="E103" s="72"/>
-      <c r="F103" s="73"/>
-      <c r="G103" s="74"/>
+      <c r="E103" s="65"/>
+      <c r="F103" s="66"/>
+      <c r="G103" s="67"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B104">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="C104">
         <v>4</v>
       </c>
-      <c r="E104" s="72"/>
-      <c r="F104" s="73"/>
-      <c r="G104" s="74"/>
+      <c r="E104" s="65"/>
+      <c r="F104" s="66"/>
+      <c r="G104" s="67"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B105">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C105">
         <v>4</v>
       </c>
-      <c r="E105" s="72"/>
-      <c r="F105" s="73"/>
-      <c r="G105" s="74"/>
+      <c r="E105" s="65"/>
+      <c r="F105" s="66"/>
+      <c r="G105" s="67"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="22" t="s">
-        <v>48</v>
+      <c r="A106" s="21" t="s">
+        <v>47</v>
       </c>
       <c r="B106">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C106">
         <v>4</v>
       </c>
-      <c r="E106" s="72"/>
-      <c r="F106" s="73"/>
-      <c r="G106" s="74"/>
+      <c r="E106" s="65"/>
+      <c r="F106" s="66"/>
+      <c r="G106" s="67"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="21" t="s">
-        <v>49</v>
+      <c r="A107" s="22" t="s">
+        <v>48</v>
       </c>
       <c r="B107">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C107">
         <v>4</v>
       </c>
-      <c r="E107" s="72"/>
-      <c r="F107" s="73"/>
-      <c r="G107" s="74"/>
+      <c r="E107" s="65"/>
+      <c r="F107" s="66"/>
+      <c r="G107" s="67"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="21" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="B108">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C108">
         <v>4</v>
       </c>
-      <c r="E108" s="72"/>
-      <c r="F108" s="73"/>
-      <c r="G108" s="74"/>
+      <c r="E108" s="65"/>
+      <c r="F108" s="66"/>
+      <c r="G108" s="67"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="79" t="s">
-        <v>50</v>
+      <c r="A109" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="B109">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C109">
         <v>4</v>
       </c>
-      <c r="E109" s="72"/>
-      <c r="F109" s="75"/>
-      <c r="G109" s="74"/>
+      <c r="E109" s="65"/>
+      <c r="F109" s="66"/>
+      <c r="G109" s="67"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E110" s="76"/>
-      <c r="F110" s="77"/>
-      <c r="G110" s="57"/>
+      <c r="A110" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="B110">
+        <v>58</v>
+      </c>
+      <c r="C110">
+        <v>4</v>
+      </c>
+      <c r="E110" s="65"/>
+      <c r="F110" s="68"/>
+      <c r="G110" s="67"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="14" t="str">
-        <f>A96</f>
+      <c r="E111" s="69"/>
+      <c r="F111" s="70"/>
+      <c r="G111" s="56"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="14" t="str">
+        <f>A97</f>
         <v>DELICIAS</v>
       </c>
-      <c r="B111">
+      <c r="B112">
         <v>1</v>
       </c>
-      <c r="C111">
+      <c r="C112">
         <v>4</v>
       </c>
-      <c r="E111" s="32"/>
-      <c r="F111" s="33"/>
-      <c r="G111" s="34"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="23"/>
-      <c r="G113" s="49"/>
+      <c r="E112" s="42"/>
+      <c r="F112" s="43"/>
+      <c r="G112" s="44"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E114" s="58"/>
-      <c r="F114" s="59"/>
-      <c r="G114" s="60"/>
-    </row>
-    <row r="115" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E115" s="61"/>
-      <c r="F115" s="62"/>
-      <c r="G115" s="63"/>
-    </row>
-    <row r="116" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A116" s="16" t="s">
+      <c r="A114" s="23"/>
+      <c r="G114" s="48"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E115" s="49"/>
+      <c r="F115" s="50"/>
+      <c r="G115" s="51"/>
+    </row>
+    <row r="116" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E116" s="52"/>
+      <c r="F116" s="53"/>
+      <c r="G116" s="54"/>
+    </row>
+    <row r="117" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A117" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E116" s="32"/>
-      <c r="F116" s="33"/>
-      <c r="G116" s="34"/>
-    </row>
-    <row r="117" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="14" t="s">
+      <c r="E117" s="32"/>
+      <c r="F117" s="33"/>
+      <c r="G117" s="34"/>
+    </row>
+    <row r="118" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E117" s="88"/>
-      <c r="F117" s="89"/>
-      <c r="G117" s="64"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B118">
-        <v>2</v>
-      </c>
-      <c r="C118">
-        <v>3</v>
-      </c>
-      <c r="E118" s="65"/>
-      <c r="F118" s="66"/>
-      <c r="G118" s="67"/>
+      <c r="E118" s="76"/>
+      <c r="F118" s="77"/>
+      <c r="G118" s="57"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B119">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C119">
         <v>3</v>
       </c>
-      <c r="E119" s="68"/>
-      <c r="F119" s="69"/>
-      <c r="G119" s="70"/>
+      <c r="E119" s="58"/>
+      <c r="F119" s="59"/>
+      <c r="G119" s="60"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B120">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="C120">
         <v>3</v>
       </c>
-      <c r="E120" s="68"/>
-      <c r="F120" s="69"/>
-      <c r="G120" s="70"/>
+      <c r="E120" s="61"/>
+      <c r="F120" s="62"/>
+      <c r="G120" s="63"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E121" s="90"/>
-      <c r="F121" s="91"/>
-      <c r="G121" s="92"/>
+      <c r="A121" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B121">
+        <v>61</v>
+      </c>
+      <c r="C121">
+        <v>3</v>
+      </c>
+      <c r="E121" s="61"/>
+      <c r="F121" s="62"/>
+      <c r="G121" s="63"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="14" t="str">
-        <f>A116</f>
+      <c r="E122" s="78"/>
+      <c r="F122" s="79"/>
+      <c r="G122" s="80"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="14" t="str">
+        <f>A117</f>
         <v>AHUMADA</v>
       </c>
-      <c r="B122">
+      <c r="B123">
         <v>1</v>
       </c>
-      <c r="C122">
+      <c r="C123">
         <v>3</v>
       </c>
-      <c r="E122" s="32"/>
-      <c r="F122" s="33"/>
-      <c r="G122" s="34"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E125" s="50"/>
-      <c r="F125" s="51"/>
-      <c r="G125" s="52"/>
-    </row>
-    <row r="126" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E126" s="53"/>
-      <c r="F126" s="54"/>
-      <c r="G126" s="55"/>
-    </row>
-    <row r="127" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="13" t="s">
+      <c r="E123" s="42"/>
+      <c r="F123" s="43"/>
+      <c r="G123" s="44"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E126" s="49"/>
+      <c r="F126" s="50"/>
+      <c r="G126" s="51"/>
+    </row>
+    <row r="127" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E127" s="52"/>
+      <c r="F127" s="53"/>
+      <c r="G127" s="54"/>
+    </row>
+    <row r="128" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E127" s="32"/>
-      <c r="F127" s="33"/>
-      <c r="G127" s="34"/>
-    </row>
-    <row r="128" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="14" t="s">
+      <c r="E128" s="32"/>
+      <c r="F128" s="33"/>
+      <c r="G128" s="34"/>
+    </row>
+    <row r="129" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E128" s="88"/>
-      <c r="F128" s="89"/>
-      <c r="G128" s="35"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B129">
-        <v>41</v>
-      </c>
-      <c r="C129">
-        <v>2</v>
-      </c>
-      <c r="E129" s="47"/>
-      <c r="F129" s="48"/>
-      <c r="G129" s="56"/>
+      <c r="E129" s="76"/>
+      <c r="F129" s="77"/>
+      <c r="G129" s="35"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B130">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C130">
         <v>2</v>
       </c>
-      <c r="E130" s="47"/>
-      <c r="F130" s="48"/>
-      <c r="G130" s="56"/>
+      <c r="E130" s="46"/>
+      <c r="F130" s="47"/>
+      <c r="G130" s="55"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B131">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C131">
         <v>2</v>
       </c>
-      <c r="E131" s="47"/>
-      <c r="F131" s="48"/>
-      <c r="G131" s="56"/>
+      <c r="E131" s="46"/>
+      <c r="F131" s="47"/>
+      <c r="G131" s="55"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B132">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C132">
         <v>2</v>
       </c>
-      <c r="E132" s="47"/>
-      <c r="F132" s="48"/>
-      <c r="G132" s="56"/>
+      <c r="E132" s="46"/>
+      <c r="F132" s="47"/>
+      <c r="G132" s="55"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B133">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C133">
         <v>2</v>
       </c>
-      <c r="E133" s="47"/>
-      <c r="F133" s="48"/>
-      <c r="G133" s="56"/>
+      <c r="E133" s="46"/>
+      <c r="F133" s="47"/>
+      <c r="G133" s="55"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B134">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C134">
         <v>2</v>
       </c>
-      <c r="E134" s="47"/>
-      <c r="F134" s="48"/>
-      <c r="G134" s="56"/>
+      <c r="E134" s="46"/>
+      <c r="F134" s="47"/>
+      <c r="G134" s="55"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B135">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C135">
         <v>2</v>
       </c>
-      <c r="E135" s="47"/>
-      <c r="F135" s="48"/>
-      <c r="G135" s="56"/>
+      <c r="E135" s="46"/>
+      <c r="F135" s="47"/>
+      <c r="G135" s="55"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B136">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C136">
         <v>2</v>
       </c>
-      <c r="E136" s="47"/>
-      <c r="F136" s="48"/>
-      <c r="G136" s="56"/>
+      <c r="E136" s="46"/>
+      <c r="F136" s="47"/>
+      <c r="G136" s="55"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E137" s="90"/>
-      <c r="F137" s="91"/>
-      <c r="G137" s="92"/>
+      <c r="A137" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B137">
+        <v>16</v>
+      </c>
+      <c r="C137">
+        <v>2</v>
+      </c>
+      <c r="E137" s="46"/>
+      <c r="F137" s="47"/>
+      <c r="G137" s="55"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="14" t="str">
-        <f>A127</f>
+      <c r="E138" s="78"/>
+      <c r="F138" s="79"/>
+      <c r="G138" s="80"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="14" t="str">
+        <f>A128</f>
         <v>INDEPENDENCIA</v>
       </c>
-      <c r="B138">
+      <c r="B139">
         <v>1</v>
       </c>
-      <c r="C138">
+      <c r="C139">
         <v>2</v>
       </c>
-      <c r="E138" s="32"/>
-      <c r="F138" s="33"/>
-      <c r="G138" s="34"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E141" s="58"/>
-      <c r="F141" s="59"/>
-      <c r="G141" s="60"/>
-    </row>
-    <row r="142" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E142" s="61"/>
-      <c r="F142" s="62"/>
-      <c r="G142" s="63"/>
-    </row>
-    <row r="143" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A143" s="16" t="s">
+      <c r="E139" s="42"/>
+      <c r="F139" s="43"/>
+      <c r="G139" s="44"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E142" s="49"/>
+      <c r="F142" s="50"/>
+      <c r="G142" s="51"/>
+    </row>
+    <row r="143" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E143" s="52"/>
+      <c r="F143" s="53"/>
+      <c r="G143" s="54"/>
+    </row>
+    <row r="144" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A144" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E143" s="32"/>
-      <c r="F143" s="33"/>
-      <c r="G143" s="34"/>
-    </row>
-    <row r="144" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="14" t="s">
+      <c r="E144" s="32"/>
+      <c r="F144" s="33"/>
+      <c r="G144" s="34"/>
+    </row>
+    <row r="145" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E144" s="88"/>
-      <c r="F144" s="89"/>
-      <c r="G144" s="64"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B145">
-        <v>12</v>
-      </c>
-      <c r="C145">
-        <v>5</v>
-      </c>
-      <c r="E145" s="68"/>
-      <c r="F145" s="69"/>
-      <c r="G145" s="70"/>
+      <c r="E145" s="76"/>
+      <c r="F145" s="77"/>
+      <c r="G145" s="57"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B146">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C146">
         <v>5</v>
       </c>
-      <c r="E146" s="68"/>
-      <c r="F146" s="69"/>
-      <c r="G146" s="70"/>
+      <c r="E146" s="61"/>
+      <c r="F146" s="62"/>
+      <c r="G146" s="63"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B147">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C147">
         <v>5</v>
       </c>
-      <c r="E147" s="68"/>
-      <c r="F147" s="69"/>
-      <c r="G147" s="70"/>
+      <c r="E147" s="61"/>
+      <c r="F147" s="62"/>
+      <c r="G147" s="63"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B148">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C148">
         <v>5</v>
       </c>
-      <c r="E148" s="68"/>
-      <c r="F148" s="69"/>
-      <c r="G148" s="70"/>
+      <c r="E148" s="61"/>
+      <c r="F148" s="62"/>
+      <c r="G148" s="63"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B149">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C149">
         <v>5</v>
       </c>
-      <c r="E149" s="68"/>
-      <c r="F149" s="69"/>
-      <c r="G149" s="70"/>
+      <c r="E149" s="61"/>
+      <c r="F149" s="62"/>
+      <c r="G149" s="63"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="17" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="B150">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C150">
         <v>5</v>
       </c>
-      <c r="E150" s="68"/>
-      <c r="F150" s="69"/>
-      <c r="G150" s="70"/>
+      <c r="E150" s="61"/>
+      <c r="F150" s="62"/>
+      <c r="G150" s="63"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="B151">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C151">
         <v>5</v>
       </c>
-      <c r="E151" s="68"/>
-      <c r="F151" s="69"/>
-      <c r="G151" s="70"/>
+      <c r="E151" s="61"/>
+      <c r="F151" s="62"/>
+      <c r="G151" s="63"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B152">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C152">
         <v>5</v>
       </c>
-      <c r="E152" s="68"/>
-      <c r="F152" s="69"/>
-      <c r="G152" s="70"/>
+      <c r="E152" s="61"/>
+      <c r="F152" s="62"/>
+      <c r="G152" s="63"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E153" s="90"/>
-      <c r="F153" s="91"/>
-      <c r="G153" s="92"/>
+      <c r="A153" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B153">
+        <v>18</v>
+      </c>
+      <c r="C153">
+        <v>5</v>
+      </c>
+      <c r="E153" s="61"/>
+      <c r="F153" s="62"/>
+      <c r="G153" s="63"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="14" t="str">
-        <f>A143</f>
+      <c r="E154" s="78"/>
+      <c r="F154" s="79"/>
+      <c r="G154" s="80"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="14" t="str">
+        <f>A144</f>
         <v>CASTAÑO</v>
       </c>
-      <c r="B154">
+      <c r="B155">
         <v>1</v>
       </c>
-      <c r="C154">
+      <c r="C155">
         <v>5</v>
       </c>
-      <c r="E154" s="32"/>
-      <c r="F154" s="33"/>
-      <c r="G154" s="34"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E157" s="50"/>
-      <c r="F157" s="51"/>
-      <c r="G157" s="52"/>
-    </row>
-    <row r="158" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E158" s="53"/>
-      <c r="F158" s="54"/>
-      <c r="G158" s="55"/>
-    </row>
-    <row r="159" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A159" s="16" t="s">
+      <c r="E155" s="42"/>
+      <c r="F155" s="43"/>
+      <c r="G155" s="44"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E158" s="49"/>
+      <c r="F158" s="50"/>
+      <c r="G158" s="51"/>
+    </row>
+    <row r="159" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E159" s="52"/>
+      <c r="F159" s="53"/>
+      <c r="G159" s="54"/>
+    </row>
+    <row r="160" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A160" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E159" s="32"/>
-      <c r="F159" s="33"/>
-      <c r="G159" s="34"/>
-    </row>
-    <row r="160" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="14" t="s">
+      <c r="E160" s="32"/>
+      <c r="F160" s="33"/>
+      <c r="G160" s="34"/>
+    </row>
+    <row r="161" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E160" s="93"/>
-      <c r="F160" s="94"/>
-      <c r="G160" s="64"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="B161">
-        <v>65</v>
-      </c>
-      <c r="C161">
-        <v>11</v>
-      </c>
-      <c r="E161" s="47"/>
-      <c r="F161" s="48"/>
-      <c r="G161" s="56"/>
+      <c r="E161" s="81"/>
+      <c r="F161" s="82"/>
+      <c r="G161" s="57"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="17" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="B162">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C162">
         <v>11</v>
       </c>
-      <c r="E162" s="47"/>
-      <c r="F162" s="48"/>
-      <c r="G162" s="56"/>
+      <c r="E162" s="46"/>
+      <c r="F162" s="47"/>
+      <c r="G162" s="55"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B163">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C163">
         <v>11</v>
       </c>
-      <c r="E163" s="47"/>
-      <c r="F163" s="48"/>
-      <c r="G163" s="56"/>
+      <c r="E163" s="46"/>
+      <c r="F163" s="47"/>
+      <c r="G163" s="55"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B164">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C164">
         <v>11</v>
       </c>
-      <c r="E164" s="47"/>
-      <c r="F164" s="48"/>
-      <c r="G164" s="56"/>
+      <c r="E164" s="46"/>
+      <c r="F164" s="47"/>
+      <c r="G164" s="55"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B165">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C165">
         <v>11</v>
       </c>
-      <c r="E165" s="47"/>
-      <c r="F165" s="48"/>
-      <c r="G165" s="56"/>
+      <c r="E165" s="46"/>
+      <c r="F165" s="47"/>
+      <c r="G165" s="55"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="17"/>
-      <c r="E166" s="47"/>
-      <c r="F166" s="48"/>
-      <c r="G166" s="56"/>
+      <c r="A166" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B166">
+        <v>68</v>
+      </c>
+      <c r="C166">
+        <v>11</v>
+      </c>
+      <c r="E166" s="46"/>
+      <c r="F166" s="47"/>
+      <c r="G166" s="55"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E167" s="90"/>
-      <c r="F167" s="91"/>
-      <c r="G167" s="92"/>
-    </row>
-    <row r="168" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A168" s="80" t="str">
-        <f>A159</f>
+      <c r="A167" s="17"/>
+      <c r="E167" s="46"/>
+      <c r="F167" s="47"/>
+      <c r="G167" s="55"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E168" s="78"/>
+      <c r="F168" s="79"/>
+      <c r="G168" s="80"/>
+    </row>
+    <row r="169" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A169" s="73" t="str">
+        <f>A160</f>
         <v>San Rafael</v>
       </c>
-      <c r="B168">
+      <c r="B169">
         <v>1</v>
       </c>
-      <c r="C168">
+      <c r="C169">
         <v>11</v>
       </c>
-      <c r="E168" s="43"/>
-      <c r="F168" s="44"/>
-      <c r="G168" s="45"/>
-    </row>
-    <row r="169" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A169" s="80"/>
-      <c r="E169" s="78"/>
-      <c r="F169" s="78"/>
-      <c r="G169" s="78"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E171" s="50"/>
-      <c r="F171" s="51"/>
-      <c r="G171" s="52"/>
-    </row>
-    <row r="172" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E172" s="53"/>
-      <c r="F172" s="54"/>
-      <c r="G172" s="55"/>
-    </row>
-    <row r="173" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A173" s="16" t="s">
+      <c r="E169" s="42"/>
+      <c r="F169" s="43"/>
+      <c r="G169" s="44"/>
+    </row>
+    <row r="170" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A170" s="73"/>
+      <c r="E170" s="71"/>
+      <c r="F170" s="71"/>
+      <c r="G170" s="71"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E172" s="49"/>
+      <c r="F172" s="50"/>
+      <c r="G172" s="51"/>
+    </row>
+    <row r="173" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E173" s="52"/>
+      <c r="F173" s="53"/>
+      <c r="G173" s="54"/>
+    </row>
+    <row r="174" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A174" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E173" s="32"/>
-      <c r="F173" s="33"/>
-      <c r="G173" s="34"/>
-    </row>
-    <row r="174" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="14" t="s">
+      <c r="E174" s="32"/>
+      <c r="F174" s="33"/>
+      <c r="G174" s="34"/>
+    </row>
+    <row r="175" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E174" s="93"/>
-      <c r="F174" s="94"/>
-      <c r="G174" s="64"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B175">
-        <v>81</v>
-      </c>
-      <c r="C175">
-        <v>12</v>
-      </c>
-      <c r="E175" s="47"/>
-      <c r="F175" s="48"/>
-      <c r="G175" s="56"/>
+      <c r="E175" s="81"/>
+      <c r="F175" s="82"/>
+      <c r="G175" s="57"/>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B176">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C176">
         <v>12</v>
       </c>
-      <c r="E176" s="47"/>
-      <c r="F176" s="48"/>
-      <c r="G176" s="56"/>
+      <c r="E176" s="46"/>
+      <c r="F176" s="47"/>
+      <c r="G176" s="55"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="15" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B177">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C177">
         <v>12</v>
       </c>
-      <c r="E177" s="47"/>
-      <c r="F177" s="48"/>
-      <c r="G177" s="56"/>
+      <c r="E177" s="46"/>
+      <c r="F177" s="47"/>
+      <c r="G177" s="55"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="15" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="B178">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C178">
         <v>12</v>
       </c>
-      <c r="E178" s="47"/>
-      <c r="F178" s="48"/>
-      <c r="G178" s="56"/>
+      <c r="E178" s="46"/>
+      <c r="F178" s="47"/>
+      <c r="G178" s="55"/>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E179" s="90"/>
-      <c r="F179" s="91"/>
-      <c r="G179" s="92"/>
-    </row>
-    <row r="180" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A180" s="80" t="str">
-        <f>A173</f>
+      <c r="A179" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B179">
+        <v>72</v>
+      </c>
+      <c r="C179">
+        <v>12</v>
+      </c>
+      <c r="E179" s="46"/>
+      <c r="F179" s="47"/>
+      <c r="G179" s="55"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E180" s="78"/>
+      <c r="F180" s="79"/>
+      <c r="G180" s="80"/>
+    </row>
+    <row r="181" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A181" s="73" t="str">
+        <f>A174</f>
         <v>Puertecito</v>
       </c>
-      <c r="B180">
+      <c r="B181">
         <v>1</v>
       </c>
-      <c r="C180">
+      <c r="C181">
         <v>12</v>
       </c>
-      <c r="E180" s="43"/>
-      <c r="F180" s="44"/>
-      <c r="G180" s="45"/>
-    </row>
-    <row r="181" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A181" s="80"/>
-      <c r="E181" s="78"/>
-      <c r="F181" s="78"/>
-      <c r="G181" s="78"/>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E183" s="50"/>
-      <c r="F183" s="51"/>
-      <c r="G183" s="52"/>
-    </row>
-    <row r="184" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E184" s="53"/>
-      <c r="F184" s="54"/>
-      <c r="G184" s="55"/>
-    </row>
-    <row r="185" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A185" s="16" t="s">
+      <c r="E181" s="42"/>
+      <c r="F181" s="43"/>
+      <c r="G181" s="44"/>
+    </row>
+    <row r="182" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A182" s="73"/>
+      <c r="E182" s="71"/>
+      <c r="F182" s="71"/>
+      <c r="G182" s="71"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E184" s="49"/>
+      <c r="F184" s="50"/>
+      <c r="G184" s="51"/>
+    </row>
+    <row r="185" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E185" s="52"/>
+      <c r="F185" s="53"/>
+      <c r="G185" s="54"/>
+    </row>
+    <row r="186" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A186" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E185" s="32"/>
-      <c r="F185" s="33"/>
-      <c r="G185" s="34"/>
-    </row>
-    <row r="186" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="14" t="s">
+      <c r="E186" s="32"/>
+      <c r="F186" s="33"/>
+      <c r="G186" s="34"/>
+    </row>
+    <row r="187" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E186" s="93"/>
-      <c r="F186" s="94"/>
-      <c r="G186" s="64"/>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B187">
-        <v>73</v>
-      </c>
-      <c r="C187">
-        <v>13</v>
-      </c>
-      <c r="E187" s="47"/>
-      <c r="F187" s="48"/>
-      <c r="G187" s="56"/>
+      <c r="E187" s="81"/>
+      <c r="F187" s="82"/>
+      <c r="G187" s="57"/>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B188">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C188">
         <v>13</v>
       </c>
-      <c r="E188" s="47"/>
-      <c r="F188" s="48"/>
-      <c r="G188" s="56"/>
+      <c r="E188" s="46"/>
+      <c r="F188" s="47"/>
+      <c r="G188" s="55"/>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B189">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C189">
         <v>13</v>
       </c>
-      <c r="E189" s="47"/>
-      <c r="F189" s="48"/>
-      <c r="G189" s="56"/>
+      <c r="E189" s="46"/>
+      <c r="F189" s="47"/>
+      <c r="G189" s="55"/>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="15" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="B190">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C190">
         <v>13</v>
       </c>
-      <c r="E190" s="47"/>
-      <c r="F190" s="48"/>
-      <c r="G190" s="56"/>
+      <c r="E190" s="46"/>
+      <c r="F190" s="47"/>
+      <c r="G190" s="55"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="15" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="B191">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C191">
         <v>13</v>
       </c>
-      <c r="E191" s="47"/>
-      <c r="F191" s="48"/>
-      <c r="G191" s="56"/>
+      <c r="E191" s="46"/>
+      <c r="F191" s="47"/>
+      <c r="G191" s="55"/>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E192" s="90"/>
-      <c r="F192" s="91"/>
-      <c r="G192" s="92"/>
-    </row>
-    <row r="193" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A193" s="80" t="str">
-        <f>A185</f>
+      <c r="A192" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B192">
+        <v>75</v>
+      </c>
+      <c r="C192">
+        <v>13</v>
+      </c>
+      <c r="E192" s="46"/>
+      <c r="F192" s="47"/>
+      <c r="G192" s="55"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E193" s="78"/>
+      <c r="F193" s="79"/>
+      <c r="G193" s="80"/>
+    </row>
+    <row r="194" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A194" s="73" t="str">
+        <f>A186</f>
         <v>Colosio</v>
       </c>
-      <c r="B193">
+      <c r="B194">
         <v>1</v>
       </c>
-      <c r="C193">
+      <c r="C194">
         <v>13</v>
       </c>
-      <c r="E193" s="43"/>
-      <c r="F193" s="44"/>
-      <c r="G193" s="45"/>
-    </row>
-    <row r="194" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A194"/>
-      <c r="E194"/>
-      <c r="F194"/>
-      <c r="G194"/>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E196" s="50"/>
-      <c r="F196" s="51"/>
-      <c r="G196" s="52"/>
-    </row>
-    <row r="197" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E197" s="53"/>
-      <c r="F197" s="54"/>
-      <c r="G197" s="55"/>
-    </row>
-    <row r="198" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A198" s="16" t="s">
+      <c r="E194" s="42"/>
+      <c r="F194" s="43"/>
+      <c r="G194" s="44"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195"/>
+      <c r="E195"/>
+      <c r="F195" s="71"/>
+      <c r="G195"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E197" s="49"/>
+      <c r="F197" s="50"/>
+      <c r="G197" s="51"/>
+    </row>
+    <row r="198" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E198" s="52"/>
+      <c r="F198" s="53"/>
+      <c r="G198" s="54"/>
+    </row>
+    <row r="199" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A199" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E198" s="32"/>
-      <c r="F198" s="33"/>
-      <c r="G198" s="34"/>
-    </row>
-    <row r="199" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="14" t="s">
+      <c r="E199" s="32"/>
+      <c r="F199" s="33"/>
+      <c r="G199" s="34"/>
+    </row>
+    <row r="200" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E199" s="93"/>
-      <c r="F199" s="94"/>
-      <c r="G199" s="64"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A200" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B200">
-        <v>76</v>
-      </c>
-      <c r="C200">
-        <v>14</v>
-      </c>
-      <c r="E200" s="47"/>
-      <c r="F200" s="48"/>
-      <c r="G200" s="56"/>
+      <c r="E200" s="81"/>
+      <c r="F200" s="82"/>
+      <c r="G200" s="57"/>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B201">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C201">
         <v>14</v>
       </c>
-      <c r="E201" s="47"/>
-      <c r="F201" s="48"/>
-      <c r="G201" s="56"/>
+      <c r="E201" s="46"/>
+      <c r="F201" s="47"/>
+      <c r="G201" s="55"/>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B202">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C202">
         <v>14</v>
       </c>
-      <c r="E202" s="47"/>
-      <c r="F202" s="48"/>
-      <c r="G202" s="56"/>
+      <c r="E202" s="46"/>
+      <c r="F202" s="47"/>
+      <c r="G202" s="55"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="15" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B203">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C203">
         <v>14</v>
       </c>
-      <c r="E203" s="47"/>
-      <c r="F203" s="48"/>
-      <c r="G203" s="56"/>
+      <c r="E203" s="46"/>
+      <c r="F203" s="47"/>
+      <c r="G203" s="55"/>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E204" s="90"/>
-      <c r="F204" s="91"/>
-      <c r="G204" s="92"/>
-    </row>
-    <row r="205" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A205" s="80" t="str">
-        <f>A198</f>
+      <c r="A204" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B204">
+        <v>79</v>
+      </c>
+      <c r="C204">
+        <v>14</v>
+      </c>
+      <c r="E204" s="46"/>
+      <c r="F204" s="47"/>
+      <c r="G204" s="55"/>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E205" s="78"/>
+      <c r="F205" s="79"/>
+      <c r="G205" s="80"/>
+    </row>
+    <row r="206" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A206" s="73" t="str">
+        <f>A199</f>
         <v xml:space="preserve">Jesus Maria </v>
       </c>
-      <c r="B205">
+      <c r="B206">
         <v>1</v>
       </c>
-      <c r="C205">
+      <c r="C206">
         <v>14</v>
       </c>
-      <c r="E205" s="43"/>
-      <c r="F205" s="44"/>
-      <c r="G205" s="45"/>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E208" s="50"/>
-      <c r="F208" s="51"/>
-      <c r="G208" s="52"/>
-    </row>
-    <row r="209" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E209" s="53"/>
-      <c r="F209" s="54"/>
-      <c r="G209" s="55"/>
-    </row>
-    <row r="210" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A210" s="16" t="s">
+      <c r="E206" s="42"/>
+      <c r="F206" s="43"/>
+      <c r="G206" s="44"/>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E209" s="49"/>
+      <c r="F209" s="50"/>
+      <c r="G209" s="51"/>
+    </row>
+    <row r="210" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E210" s="52"/>
+      <c r="F210" s="53"/>
+      <c r="G210" s="54"/>
+    </row>
+    <row r="211" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A211" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="E210" s="32"/>
-      <c r="F210" s="33"/>
-      <c r="G210" s="34"/>
-    </row>
-    <row r="211" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="14" t="s">
+      <c r="E211" s="32"/>
+      <c r="F211" s="33"/>
+      <c r="G211" s="34"/>
+    </row>
+    <row r="212" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E211" s="93"/>
-      <c r="F211" s="94"/>
-      <c r="G211" s="64"/>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A212" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B212">
-        <v>87</v>
-      </c>
-      <c r="C212">
-        <v>16</v>
-      </c>
-      <c r="E212" s="47"/>
-      <c r="F212" s="48"/>
-      <c r="G212" s="56"/>
+      <c r="E212" s="81"/>
+      <c r="F212" s="82"/>
+      <c r="G212" s="57"/>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B213">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C213">
         <v>16</v>
       </c>
-      <c r="E213" s="47"/>
-      <c r="F213" s="48"/>
-      <c r="G213" s="56"/>
+      <c r="E213" s="46"/>
+      <c r="F213" s="47"/>
+      <c r="G213" s="55"/>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B214">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C214">
         <v>16</v>
       </c>
-      <c r="E214" s="47"/>
-      <c r="F214" s="48"/>
-      <c r="G214" s="56"/>
+      <c r="E214" s="46"/>
+      <c r="F214" s="47"/>
+      <c r="G214" s="55"/>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B215">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C215">
         <v>16</v>
       </c>
-      <c r="E215" s="47"/>
-      <c r="F215" s="48"/>
-      <c r="G215" s="56"/>
+      <c r="E215" s="46"/>
+      <c r="F215" s="47"/>
+      <c r="G215" s="55"/>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E216" s="90"/>
-      <c r="F216" s="91"/>
-      <c r="G216" s="92"/>
-    </row>
-    <row r="217" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A217" s="80" t="str">
-        <f>A210</f>
+      <c r="A216" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B216">
+        <v>90</v>
+      </c>
+      <c r="C216">
+        <v>16</v>
+      </c>
+      <c r="E216" s="46"/>
+      <c r="F216" s="47"/>
+      <c r="G216" s="55"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E217" s="78"/>
+      <c r="F217" s="79"/>
+      <c r="G217" s="80"/>
+    </row>
+    <row r="218" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A218" s="73" t="str">
+        <f>A211</f>
         <v xml:space="preserve">Gabriela Mistral </v>
       </c>
-      <c r="B217">
+      <c r="B218">
         <v>1</v>
       </c>
-      <c r="C217">
+      <c r="C218">
         <v>16</v>
       </c>
-      <c r="E217" s="43"/>
-      <c r="F217" s="44"/>
-      <c r="G217" s="45"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E220" s="50"/>
-      <c r="F220" s="51"/>
-      <c r="G220" s="52"/>
-    </row>
-    <row r="221" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E221" s="53"/>
-      <c r="F221" s="54"/>
-      <c r="G221" s="55"/>
-    </row>
-    <row r="222" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A222" s="16" t="s">
+      <c r="E218" s="42"/>
+      <c r="F218" s="43"/>
+      <c r="G218" s="44"/>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E221" s="49"/>
+      <c r="F221" s="50"/>
+      <c r="G221" s="51"/>
+    </row>
+    <row r="222" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E222" s="52"/>
+      <c r="F222" s="53"/>
+      <c r="G222" s="54"/>
+    </row>
+    <row r="223" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A223" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E222" s="32"/>
-      <c r="F222" s="33"/>
-      <c r="G222" s="34"/>
-    </row>
-    <row r="223" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="14" t="s">
+      <c r="E223" s="32"/>
+      <c r="F223" s="33"/>
+      <c r="G223" s="34"/>
+    </row>
+    <row r="224" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E223" s="93"/>
-      <c r="F223" s="94"/>
-      <c r="G223" s="64"/>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A224" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B224">
-        <v>11</v>
-      </c>
-      <c r="C224">
-        <v>7</v>
-      </c>
-      <c r="E224" s="47"/>
-      <c r="F224" s="48"/>
-      <c r="G224" s="56"/>
+      <c r="E224" s="81"/>
+      <c r="F224" s="82"/>
+      <c r="G224" s="57"/>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="17" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="B225">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="C225">
         <v>7</v>
       </c>
-      <c r="E225" s="47"/>
-      <c r="F225" s="48"/>
-      <c r="G225" s="56"/>
+      <c r="E225" s="46"/>
+      <c r="F225" s="47"/>
+      <c r="G225" s="55"/>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B226">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C226">
         <v>7</v>
       </c>
-      <c r="E226" s="47"/>
-      <c r="F226" s="48"/>
-      <c r="G226" s="56"/>
+      <c r="E226" s="46"/>
+      <c r="F226" s="47"/>
+      <c r="G226" s="55"/>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A227" s="17"/>
-      <c r="E227" s="47"/>
-      <c r="F227" s="48"/>
-      <c r="G227" s="56"/>
+      <c r="A227" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B227">
+        <v>51</v>
+      </c>
+      <c r="C227">
+        <v>7</v>
+      </c>
+      <c r="E227" s="46"/>
+      <c r="F227" s="47"/>
+      <c r="G227" s="55"/>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E228" s="90"/>
-      <c r="F228" s="91"/>
-      <c r="G228" s="92"/>
+      <c r="A228" s="17"/>
+      <c r="E228" s="46"/>
+      <c r="F228" s="47"/>
+      <c r="G228" s="55"/>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A229" s="14" t="str">
-        <f>A222</f>
+      <c r="E229" s="78"/>
+      <c r="F229" s="79"/>
+      <c r="G229" s="80"/>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="14" t="str">
+        <f>A223</f>
         <v xml:space="preserve">PICACHOS </v>
       </c>
-      <c r="B229">
+      <c r="B230">
         <v>1</v>
       </c>
-      <c r="C229">
+      <c r="C230">
         <v>7</v>
       </c>
-      <c r="E229" s="32"/>
-      <c r="F229" s="33"/>
-      <c r="G229" s="34"/>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A232" s="14"/>
-      <c r="E232" s="50"/>
-      <c r="F232" s="51"/>
-      <c r="G232" s="52"/>
-    </row>
-    <row r="233" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E233" s="53"/>
-      <c r="F233" s="54"/>
-      <c r="G233" s="55"/>
-    </row>
-    <row r="234" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A234" s="16" t="s">
+      <c r="E230" s="42"/>
+      <c r="F230" s="43"/>
+      <c r="G230" s="44"/>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="14"/>
+      <c r="E233" s="49"/>
+      <c r="F233" s="50"/>
+      <c r="G233" s="51"/>
+    </row>
+    <row r="234" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E234" s="52"/>
+      <c r="F234" s="53"/>
+      <c r="G234" s="54"/>
+    </row>
+    <row r="235" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A235" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E234" s="32"/>
-      <c r="F234" s="33"/>
-      <c r="G234" s="34"/>
-    </row>
-    <row r="235" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="14" t="s">
+      <c r="E235" s="32"/>
+      <c r="F235" s="33"/>
+      <c r="G235" s="34"/>
+    </row>
+    <row r="236" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E235" s="88"/>
-      <c r="F235" s="89"/>
-      <c r="G235" s="64"/>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A236" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B236">
-        <v>19</v>
-      </c>
-      <c r="C236">
-        <v>9</v>
-      </c>
-      <c r="E236" s="47"/>
-      <c r="F236" s="48"/>
-      <c r="G236" s="56"/>
+      <c r="E236" s="76"/>
+      <c r="F236" s="77"/>
+      <c r="G236" s="57"/>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B237">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C237">
         <v>9</v>
       </c>
-      <c r="E237" s="47"/>
-      <c r="F237" s="48"/>
-      <c r="G237" s="56"/>
+      <c r="E237" s="46"/>
+      <c r="F237" s="47"/>
+      <c r="G237" s="55"/>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A238" s="17"/>
-      <c r="E238" s="47"/>
-      <c r="F238" s="48"/>
-      <c r="G238" s="56"/>
+      <c r="A238" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B238">
+        <v>17</v>
+      </c>
+      <c r="C238">
+        <v>9</v>
+      </c>
+      <c r="E238" s="46"/>
+      <c r="F238" s="47"/>
+      <c r="G238" s="55"/>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="17"/>
-      <c r="E239" s="47"/>
-      <c r="F239" s="48"/>
-      <c r="G239" s="56"/>
+      <c r="E239" s="46"/>
+      <c r="F239" s="47"/>
+      <c r="G239" s="55"/>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E240" s="90"/>
-      <c r="F240" s="91"/>
-      <c r="G240" s="92"/>
+      <c r="A240" s="17"/>
+      <c r="E240" s="46"/>
+      <c r="F240" s="47"/>
+      <c r="G240" s="55"/>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A241" s="14" t="str">
-        <f>A234</f>
+      <c r="E241" s="78"/>
+      <c r="F241" s="79"/>
+      <c r="G241" s="80"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" s="14" t="str">
+        <f>A235</f>
         <v>VENTANAS</v>
       </c>
-      <c r="B241">
+      <c r="B242">
         <v>1</v>
       </c>
-      <c r="C241">
+      <c r="C242">
         <v>9</v>
       </c>
-      <c r="E241" s="32"/>
-      <c r="F241" s="33"/>
-      <c r="G241" s="34"/>
+      <c r="E242" s="42"/>
+      <c r="F242" s="43"/>
+      <c r="G242" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="E138:G138"/>
+    <mergeCell ref="E241:G241"/>
+    <mergeCell ref="E175:F175"/>
+    <mergeCell ref="E180:G180"/>
+    <mergeCell ref="E187:F187"/>
+    <mergeCell ref="E193:G193"/>
+    <mergeCell ref="E200:F200"/>
+    <mergeCell ref="E236:F236"/>
+    <mergeCell ref="E205:G205"/>
+    <mergeCell ref="E212:F212"/>
+    <mergeCell ref="E217:G217"/>
+    <mergeCell ref="E224:F224"/>
+    <mergeCell ref="E229:G229"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="E154:G154"/>
+    <mergeCell ref="E161:F161"/>
+    <mergeCell ref="E168:G168"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="E42:F42"/>
     <mergeCell ref="E48:G48"/>
     <mergeCell ref="E55:F55"/>
@@ -3981,27 +3963,9 @@
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="E72:G72"/>
     <mergeCell ref="E80:F80"/>
-    <mergeCell ref="E90:G90"/>
-    <mergeCell ref="E192:G192"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="E137:G137"/>
-    <mergeCell ref="E144:F144"/>
-    <mergeCell ref="E153:G153"/>
-    <mergeCell ref="E160:F160"/>
-    <mergeCell ref="E167:G167"/>
-    <mergeCell ref="E174:F174"/>
-    <mergeCell ref="E179:G179"/>
-    <mergeCell ref="E186:F186"/>
-    <mergeCell ref="E235:F235"/>
-    <mergeCell ref="E240:G240"/>
-    <mergeCell ref="E199:F199"/>
-    <mergeCell ref="E204:G204"/>
-    <mergeCell ref="E211:F211"/>
-    <mergeCell ref="E216:G216"/>
-    <mergeCell ref="E223:F223"/>
-    <mergeCell ref="E228:G228"/>
+    <mergeCell ref="E91:G91"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E98:F98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/_assets/includes/documents/FormatoPrecio.xlsx
+++ b/_assets/includes/documents/FormatoPrecio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alejandro.martinez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0750B068-7B15-44D8-A1B9-897F36CF479A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651CF708-24EE-490B-A61E-C776F15075D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{57A7AD68-8712-49E5-8AAC-8C9DF7ECE3A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{57A7AD68-8712-49E5-8AAC-8C9DF7ECE3A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="119">
   <si>
     <t>precio pemex</t>
   </si>
@@ -361,9 +361,6 @@
   </si>
   <si>
     <t>San Rafael</t>
-  </si>
-  <si>
-    <t>SERVICIOS GASOLINEROS OXXO  PL/9791/EXP/ES/2015  .890</t>
   </si>
   <si>
     <t>SERVICIO AVENIDA VALERO  PL/724/EXP/ES/2015  .900</t>
@@ -1690,9 +1687,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{E7F0BE38-5E70-4052-90AF-7E7CADA3CBCA}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;f94d7d05-9462-468e-b1e6-87b0ef2c7687&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97394460-1E87-45F2-A434-F65D90B57D24}">
-  <dimension ref="A1:G242"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="77" style="10" bestFit="1" customWidth="1"/>
@@ -1740,7 +1759,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5" s="32"/>
       <c r="F5" s="33"/>
@@ -1756,7 +1775,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" s="32"/>
       <c r="F7" s="33"/>
@@ -1764,7 +1783,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E8" s="32"/>
       <c r="F8" s="33"/>
@@ -1780,7 +1799,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="33"/>
@@ -1788,7 +1807,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E11" s="32"/>
       <c r="F11" s="33"/>
@@ -1796,7 +1815,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="33"/>
@@ -1995,7 +2014,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="33"/>
@@ -2003,7 +2022,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="33"/>
@@ -2019,7 +2038,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E33" s="32"/>
       <c r="F33" s="33"/>
@@ -2027,7 +2046,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="33"/>
@@ -2035,7 +2054,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="74" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="33"/>
@@ -2293,7 +2312,7 @@
     </row>
     <row r="67" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A67" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E67" s="32"/>
       <c r="F67" s="33"/>
@@ -2309,7 +2328,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B69">
         <v>84</v>
@@ -2323,7 +2342,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B70">
         <v>85</v>
@@ -2509,7 +2528,7 @@
     </row>
     <row r="89" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B89" s="10">
         <v>92</v>
@@ -2637,7 +2656,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B102">
         <v>91</v>
@@ -2735,7 +2754,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B109">
         <v>86</v>
@@ -3129,7 +3148,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B151">
         <v>13</v>
@@ -3217,7 +3236,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B162">
         <v>65</v>
@@ -3234,7 +3253,7 @@
         <v>80</v>
       </c>
       <c r="B163">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C163">
         <v>11</v>
@@ -3248,7 +3267,7 @@
         <v>81</v>
       </c>
       <c r="B164">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C164">
         <v>11</v>
@@ -3262,7 +3281,7 @@
         <v>82</v>
       </c>
       <c r="B165">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C165">
         <v>11</v>
@@ -3272,83 +3291,91 @@
       <c r="G165" s="55"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B166">
-        <v>68</v>
-      </c>
-      <c r="C166">
-        <v>11</v>
-      </c>
-      <c r="E166" s="46"/>
-      <c r="F166" s="47"/>
-      <c r="G166" s="55"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="17"/>
-      <c r="E167" s="46"/>
-      <c r="F167" s="47"/>
-      <c r="G167" s="55"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E168" s="78"/>
-      <c r="F168" s="79"/>
-      <c r="G168" s="80"/>
-    </row>
-    <row r="169" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A169" s="73" t="str">
+      <c r="E166" s="78"/>
+      <c r="F166" s="79"/>
+      <c r="G166" s="80"/>
+    </row>
+    <row r="167" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A167" s="73" t="str">
         <f>A160</f>
         <v>San Rafael</v>
       </c>
-      <c r="B169">
+      <c r="B167">
         <v>1</v>
       </c>
-      <c r="C169">
+      <c r="C167">
         <v>11</v>
       </c>
-      <c r="E169" s="42"/>
-      <c r="F169" s="43"/>
-      <c r="G169" s="44"/>
-    </row>
-    <row r="170" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A170" s="73"/>
-      <c r="E170" s="71"/>
-      <c r="F170" s="71"/>
-      <c r="G170" s="71"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E172" s="49"/>
-      <c r="F172" s="50"/>
-      <c r="G172" s="51"/>
+      <c r="E167" s="42"/>
+      <c r="F167" s="43"/>
+      <c r="G167" s="44"/>
+    </row>
+    <row r="168" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A168" s="73"/>
+      <c r="E168" s="71"/>
+      <c r="F168" s="71"/>
+      <c r="G168" s="71"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E170" s="49"/>
+      <c r="F170" s="50"/>
+      <c r="G170" s="51"/>
+    </row>
+    <row r="171" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E171" s="52"/>
+      <c r="F171" s="53"/>
+      <c r="G171" s="54"/>
+    </row>
+    <row r="172" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A172" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E172" s="32"/>
+      <c r="F172" s="33"/>
+      <c r="G172" s="34"/>
     </row>
     <row r="173" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E173" s="52"/>
-      <c r="F173" s="53"/>
-      <c r="G173" s="54"/>
-    </row>
-    <row r="174" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A174" s="16" t="s">
+      <c r="A173" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E173" s="81"/>
+      <c r="F173" s="82"/>
+      <c r="G173" s="57"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E174" s="32"/>
-      <c r="F174" s="33"/>
-      <c r="G174" s="34"/>
-    </row>
-    <row r="175" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E175" s="81"/>
-      <c r="F175" s="82"/>
-      <c r="G175" s="57"/>
+      <c r="B174">
+        <v>81</v>
+      </c>
+      <c r="C174">
+        <v>12</v>
+      </c>
+      <c r="E174" s="46"/>
+      <c r="F174" s="47"/>
+      <c r="G174" s="55"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B175">
+        <v>70</v>
+      </c>
+      <c r="C175">
+        <v>12</v>
+      </c>
+      <c r="E175" s="46"/>
+      <c r="F175" s="47"/>
+      <c r="G175" s="55"/>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="15" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="B176">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C176">
         <v>12</v>
@@ -3362,7 +3389,7 @@
         <v>86</v>
       </c>
       <c r="B177">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C177">
         <v>12</v>
@@ -3372,91 +3399,91 @@
       <c r="G177" s="55"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B178">
-        <v>71</v>
-      </c>
-      <c r="C178">
-        <v>12</v>
-      </c>
-      <c r="E178" s="46"/>
-      <c r="F178" s="47"/>
-      <c r="G178" s="55"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="15" t="s">
-        <v>87</v>
+      <c r="E178" s="78"/>
+      <c r="F178" s="79"/>
+      <c r="G178" s="80"/>
+    </row>
+    <row r="179" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A179" s="73" t="str">
+        <f>A172</f>
+        <v>Puertecito</v>
       </c>
       <c r="B179">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="C179">
         <v>12</v>
       </c>
-      <c r="E179" s="46"/>
-      <c r="F179" s="47"/>
-      <c r="G179" s="55"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E180" s="78"/>
-      <c r="F180" s="79"/>
-      <c r="G180" s="80"/>
-    </row>
-    <row r="181" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A181" s="73" t="str">
-        <f>A174</f>
-        <v>Puertecito</v>
-      </c>
-      <c r="B181">
-        <v>1</v>
-      </c>
-      <c r="C181">
-        <v>12</v>
-      </c>
-      <c r="E181" s="42"/>
-      <c r="F181" s="43"/>
-      <c r="G181" s="44"/>
-    </row>
-    <row r="182" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A182" s="73"/>
-      <c r="E182" s="71"/>
-      <c r="F182" s="71"/>
-      <c r="G182" s="71"/>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E184" s="49"/>
-      <c r="F184" s="50"/>
-      <c r="G184" s="51"/>
+      <c r="E179" s="42"/>
+      <c r="F179" s="43"/>
+      <c r="G179" s="44"/>
+    </row>
+    <row r="180" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A180" s="73"/>
+      <c r="E180" s="71"/>
+      <c r="F180" s="71"/>
+      <c r="G180" s="71"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E182" s="49"/>
+      <c r="F182" s="50"/>
+      <c r="G182" s="51"/>
+    </row>
+    <row r="183" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E183" s="52"/>
+      <c r="F183" s="53"/>
+      <c r="G183" s="54"/>
+    </row>
+    <row r="184" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A184" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E184" s="32"/>
+      <c r="F184" s="33"/>
+      <c r="G184" s="34"/>
     </row>
     <row r="185" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E185" s="52"/>
-      <c r="F185" s="53"/>
-      <c r="G185" s="54"/>
-    </row>
-    <row r="186" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A186" s="16" t="s">
+      <c r="A185" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E185" s="81"/>
+      <c r="F185" s="82"/>
+      <c r="G185" s="57"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E186" s="32"/>
-      <c r="F186" s="33"/>
-      <c r="G186" s="34"/>
-    </row>
-    <row r="187" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E187" s="81"/>
-      <c r="F187" s="82"/>
-      <c r="G187" s="57"/>
+      <c r="B186">
+        <v>73</v>
+      </c>
+      <c r="C186">
+        <v>13</v>
+      </c>
+      <c r="E186" s="46"/>
+      <c r="F186" s="47"/>
+      <c r="G186" s="55"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B187">
+        <v>74</v>
+      </c>
+      <c r="C187">
+        <v>13</v>
+      </c>
+      <c r="E187" s="46"/>
+      <c r="F187" s="47"/>
+      <c r="G187" s="55"/>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="15" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B188">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C188">
         <v>13</v>
@@ -3467,10 +3494,10 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="15" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="B189">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C189">
         <v>13</v>
@@ -3481,10 +3508,10 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="15" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B190">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C190">
         <v>13</v>
@@ -3494,91 +3521,91 @@
       <c r="G190" s="55"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A191" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B191">
-        <v>83</v>
-      </c>
-      <c r="C191">
-        <v>13</v>
-      </c>
-      <c r="E191" s="46"/>
-      <c r="F191" s="47"/>
-      <c r="G191" s="55"/>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="15" t="s">
-        <v>91</v>
+      <c r="E191" s="78"/>
+      <c r="F191" s="79"/>
+      <c r="G191" s="80"/>
+    </row>
+    <row r="192" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A192" s="73" t="str">
+        <f>A184</f>
+        <v>Colosio</v>
       </c>
       <c r="B192">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="C192">
         <v>13</v>
       </c>
-      <c r="E192" s="46"/>
-      <c r="F192" s="47"/>
-      <c r="G192" s="55"/>
+      <c r="E192" s="42"/>
+      <c r="F192" s="43"/>
+      <c r="G192" s="44"/>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E193" s="78"/>
-      <c r="F193" s="79"/>
-      <c r="G193" s="80"/>
-    </row>
-    <row r="194" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A194" s="73" t="str">
-        <f>A186</f>
-        <v>Colosio</v>
-      </c>
-      <c r="B194">
-        <v>1</v>
-      </c>
-      <c r="C194">
-        <v>13</v>
-      </c>
-      <c r="E194" s="42"/>
-      <c r="F194" s="43"/>
-      <c r="G194" s="44"/>
+      <c r="A193"/>
+      <c r="E193"/>
+      <c r="F193" s="71"/>
+      <c r="G193"/>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A195"/>
-      <c r="E195"/>
-      <c r="F195" s="71"/>
-      <c r="G195"/>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E197" s="49"/>
-      <c r="F197" s="50"/>
-      <c r="G197" s="51"/>
+      <c r="E195" s="49"/>
+      <c r="F195" s="50"/>
+      <c r="G195" s="51"/>
+    </row>
+    <row r="196" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E196" s="52"/>
+      <c r="F196" s="53"/>
+      <c r="G196" s="54"/>
+    </row>
+    <row r="197" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A197" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E197" s="32"/>
+      <c r="F197" s="33"/>
+      <c r="G197" s="34"/>
     </row>
     <row r="198" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E198" s="52"/>
-      <c r="F198" s="53"/>
-      <c r="G198" s="54"/>
-    </row>
-    <row r="199" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A199" s="16" t="s">
+      <c r="A198" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E198" s="81"/>
+      <c r="F198" s="82"/>
+      <c r="G198" s="57"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E199" s="32"/>
-      <c r="F199" s="33"/>
-      <c r="G199" s="34"/>
-    </row>
-    <row r="200" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E200" s="81"/>
-      <c r="F200" s="82"/>
-      <c r="G200" s="57"/>
+      <c r="B199">
+        <v>76</v>
+      </c>
+      <c r="C199">
+        <v>14</v>
+      </c>
+      <c r="E199" s="46"/>
+      <c r="F199" s="47"/>
+      <c r="G199" s="55"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B200">
+        <v>77</v>
+      </c>
+      <c r="C200">
+        <v>14</v>
+      </c>
+      <c r="E200" s="46"/>
+      <c r="F200" s="47"/>
+      <c r="G200" s="55"/>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B201">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C201">
         <v>14</v>
@@ -3589,10 +3616,10 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="15" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B202">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C202">
         <v>14</v>
@@ -3602,85 +3629,85 @@
       <c r="G202" s="55"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A203" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B203">
-        <v>78</v>
-      </c>
-      <c r="C203">
-        <v>14</v>
-      </c>
-      <c r="E203" s="46"/>
-      <c r="F203" s="47"/>
-      <c r="G203" s="55"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A204" s="15" t="s">
-        <v>111</v>
+      <c r="E203" s="78"/>
+      <c r="F203" s="79"/>
+      <c r="G203" s="80"/>
+    </row>
+    <row r="204" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A204" s="73" t="str">
+        <f>A197</f>
+        <v xml:space="preserve">Jesus Maria </v>
       </c>
       <c r="B204">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="C204">
         <v>14</v>
       </c>
-      <c r="E204" s="46"/>
-      <c r="F204" s="47"/>
-      <c r="G204" s="55"/>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E205" s="78"/>
-      <c r="F205" s="79"/>
-      <c r="G205" s="80"/>
-    </row>
-    <row r="206" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A206" s="73" t="str">
-        <f>A199</f>
-        <v xml:space="preserve">Jesus Maria </v>
-      </c>
-      <c r="B206">
-        <v>1</v>
-      </c>
-      <c r="C206">
-        <v>14</v>
-      </c>
-      <c r="E206" s="42"/>
-      <c r="F206" s="43"/>
-      <c r="G206" s="44"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E209" s="49"/>
-      <c r="F209" s="50"/>
-      <c r="G209" s="51"/>
+      <c r="E204" s="42"/>
+      <c r="F204" s="43"/>
+      <c r="G204" s="44"/>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E207" s="49"/>
+      <c r="F207" s="50"/>
+      <c r="G207" s="51"/>
+    </row>
+    <row r="208" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E208" s="52"/>
+      <c r="F208" s="53"/>
+      <c r="G208" s="54"/>
+    </row>
+    <row r="209" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A209" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E209" s="32"/>
+      <c r="F209" s="33"/>
+      <c r="G209" s="34"/>
     </row>
     <row r="210" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E210" s="52"/>
-      <c r="F210" s="53"/>
-      <c r="G210" s="54"/>
-    </row>
-    <row r="211" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A211" s="16" t="s">
+      <c r="A210" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E210" s="81"/>
+      <c r="F210" s="82"/>
+      <c r="G210" s="57"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E211" s="32"/>
-      <c r="F211" s="33"/>
-      <c r="G211" s="34"/>
-    </row>
-    <row r="212" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E212" s="81"/>
-      <c r="F212" s="82"/>
-      <c r="G212" s="57"/>
+      <c r="B211">
+        <v>87</v>
+      </c>
+      <c r="C211">
+        <v>16</v>
+      </c>
+      <c r="E211" s="46"/>
+      <c r="F211" s="47"/>
+      <c r="G211" s="55"/>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B212">
+        <v>88</v>
+      </c>
+      <c r="C212">
+        <v>16</v>
+      </c>
+      <c r="E212" s="46"/>
+      <c r="F212" s="47"/>
+      <c r="G212" s="55"/>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B213">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C213">
         <v>16</v>
@@ -3691,10 +3718,10 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B214">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C214">
         <v>16</v>
@@ -3704,85 +3731,85 @@
       <c r="G214" s="55"/>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A215" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B215">
-        <v>89</v>
-      </c>
-      <c r="C215">
-        <v>16</v>
-      </c>
-      <c r="E215" s="46"/>
-      <c r="F215" s="47"/>
-      <c r="G215" s="55"/>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A216" s="15" t="s">
-        <v>116</v>
+      <c r="E215" s="78"/>
+      <c r="F215" s="79"/>
+      <c r="G215" s="80"/>
+    </row>
+    <row r="216" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A216" s="73" t="str">
+        <f>A209</f>
+        <v xml:space="preserve">Gabriela Mistral </v>
       </c>
       <c r="B216">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="C216">
         <v>16</v>
       </c>
-      <c r="E216" s="46"/>
-      <c r="F216" s="47"/>
-      <c r="G216" s="55"/>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E217" s="78"/>
-      <c r="F217" s="79"/>
-      <c r="G217" s="80"/>
-    </row>
-    <row r="218" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A218" s="73" t="str">
-        <f>A211</f>
-        <v xml:space="preserve">Gabriela Mistral </v>
-      </c>
-      <c r="B218">
-        <v>1</v>
-      </c>
-      <c r="C218">
-        <v>16</v>
-      </c>
-      <c r="E218" s="42"/>
-      <c r="F218" s="43"/>
-      <c r="G218" s="44"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E221" s="49"/>
-      <c r="F221" s="50"/>
-      <c r="G221" s="51"/>
+      <c r="E216" s="42"/>
+      <c r="F216" s="43"/>
+      <c r="G216" s="44"/>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E219" s="49"/>
+      <c r="F219" s="50"/>
+      <c r="G219" s="51"/>
+    </row>
+    <row r="220" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E220" s="52"/>
+      <c r="F220" s="53"/>
+      <c r="G220" s="54"/>
+    </row>
+    <row r="221" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A221" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E221" s="32"/>
+      <c r="F221" s="33"/>
+      <c r="G221" s="34"/>
     </row>
     <row r="222" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E222" s="52"/>
-      <c r="F222" s="53"/>
-      <c r="G222" s="54"/>
-    </row>
-    <row r="223" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A223" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E223" s="32"/>
-      <c r="F223" s="33"/>
-      <c r="G223" s="34"/>
-    </row>
-    <row r="224" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="14" t="s">
+      <c r="A222" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E224" s="81"/>
-      <c r="F224" s="82"/>
-      <c r="G224" s="57"/>
+      <c r="E222" s="81"/>
+      <c r="F222" s="82"/>
+      <c r="G222" s="57"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B223">
+        <v>11</v>
+      </c>
+      <c r="C223">
+        <v>7</v>
+      </c>
+      <c r="E223" s="46"/>
+      <c r="F223" s="47"/>
+      <c r="G223" s="55"/>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B224">
+        <v>40</v>
+      </c>
+      <c r="C224">
+        <v>7</v>
+      </c>
+      <c r="E224" s="46"/>
+      <c r="F224" s="47"/>
+      <c r="G224" s="55"/>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="17" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="B225">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="C225">
         <v>7</v>
@@ -3792,168 +3819,136 @@
       <c r="G225" s="55"/>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A226" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B226">
-        <v>40</v>
-      </c>
-      <c r="C226">
-        <v>7</v>
-      </c>
+      <c r="A226" s="17"/>
       <c r="E226" s="46"/>
       <c r="F226" s="47"/>
       <c r="G226" s="55"/>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A227" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B227">
-        <v>51</v>
-      </c>
-      <c r="C227">
+      <c r="E227" s="78"/>
+      <c r="F227" s="79"/>
+      <c r="G227" s="80"/>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="14" t="str">
+        <f>A221</f>
+        <v xml:space="preserve">PICACHOS </v>
+      </c>
+      <c r="B228">
+        <v>1</v>
+      </c>
+      <c r="C228">
         <v>7</v>
       </c>
-      <c r="E227" s="46"/>
-      <c r="F227" s="47"/>
-      <c r="G227" s="55"/>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A228" s="17"/>
-      <c r="E228" s="46"/>
-      <c r="F228" s="47"/>
-      <c r="G228" s="55"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E229" s="78"/>
-      <c r="F229" s="79"/>
-      <c r="G229" s="80"/>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A230" s="14" t="str">
-        <f>A223</f>
-        <v xml:space="preserve">PICACHOS </v>
-      </c>
-      <c r="B230">
-        <v>1</v>
-      </c>
-      <c r="C230">
-        <v>7</v>
-      </c>
-      <c r="E230" s="42"/>
-      <c r="F230" s="43"/>
-      <c r="G230" s="44"/>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A233" s="14"/>
-      <c r="E233" s="49"/>
-      <c r="F233" s="50"/>
-      <c r="G233" s="51"/>
+      <c r="E228" s="42"/>
+      <c r="F228" s="43"/>
+      <c r="G228" s="44"/>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="14"/>
+      <c r="E231" s="49"/>
+      <c r="F231" s="50"/>
+      <c r="G231" s="51"/>
+    </row>
+    <row r="232" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E232" s="52"/>
+      <c r="F232" s="53"/>
+      <c r="G232" s="54"/>
+    </row>
+    <row r="233" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A233" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E233" s="32"/>
+      <c r="F233" s="33"/>
+      <c r="G233" s="34"/>
     </row>
     <row r="234" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E234" s="52"/>
-      <c r="F234" s="53"/>
-      <c r="G234" s="54"/>
-    </row>
-    <row r="235" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A235" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E235" s="32"/>
-      <c r="F235" s="33"/>
-      <c r="G235" s="34"/>
-    </row>
-    <row r="236" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="14" t="s">
+      <c r="A234" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E236" s="76"/>
-      <c r="F236" s="77"/>
-      <c r="G236" s="57"/>
+      <c r="E234" s="76"/>
+      <c r="F234" s="77"/>
+      <c r="G234" s="57"/>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B235">
+        <v>19</v>
+      </c>
+      <c r="C235">
+        <v>9</v>
+      </c>
+      <c r="E235" s="46"/>
+      <c r="F235" s="47"/>
+      <c r="G235" s="55"/>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B236">
+        <v>17</v>
+      </c>
+      <c r="C236">
+        <v>9</v>
+      </c>
+      <c r="E236" s="46"/>
+      <c r="F236" s="47"/>
+      <c r="G236" s="55"/>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A237" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B237">
-        <v>19</v>
-      </c>
-      <c r="C237">
-        <v>9</v>
-      </c>
+      <c r="A237" s="17"/>
       <c r="E237" s="46"/>
       <c r="F237" s="47"/>
       <c r="G237" s="55"/>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A238" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B238">
-        <v>17</v>
-      </c>
-      <c r="C238">
-        <v>9</v>
-      </c>
+      <c r="A238" s="17"/>
       <c r="E238" s="46"/>
       <c r="F238" s="47"/>
       <c r="G238" s="55"/>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A239" s="17"/>
-      <c r="E239" s="46"/>
-      <c r="F239" s="47"/>
-      <c r="G239" s="55"/>
+      <c r="E239" s="78"/>
+      <c r="F239" s="79"/>
+      <c r="G239" s="80"/>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A240" s="17"/>
-      <c r="E240" s="46"/>
-      <c r="F240" s="47"/>
-      <c r="G240" s="55"/>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E241" s="78"/>
-      <c r="F241" s="79"/>
-      <c r="G241" s="80"/>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A242" s="14" t="str">
-        <f>A235</f>
+      <c r="A240" s="14" t="str">
+        <f>A233</f>
         <v>VENTANAS</v>
       </c>
-      <c r="B242">
+      <c r="B240">
         <v>1</v>
       </c>
-      <c r="C242">
+      <c r="C240">
         <v>9</v>
       </c>
-      <c r="E242" s="42"/>
-      <c r="F242" s="43"/>
-      <c r="G242" s="44"/>
+      <c r="E240" s="42"/>
+      <c r="F240" s="43"/>
+      <c r="G240" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="E118:F118"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="E138:G138"/>
-    <mergeCell ref="E241:G241"/>
-    <mergeCell ref="E175:F175"/>
-    <mergeCell ref="E180:G180"/>
-    <mergeCell ref="E187:F187"/>
-    <mergeCell ref="E193:G193"/>
-    <mergeCell ref="E200:F200"/>
-    <mergeCell ref="E236:F236"/>
-    <mergeCell ref="E205:G205"/>
-    <mergeCell ref="E212:F212"/>
-    <mergeCell ref="E217:G217"/>
-    <mergeCell ref="E224:F224"/>
-    <mergeCell ref="E229:G229"/>
+    <mergeCell ref="E239:G239"/>
+    <mergeCell ref="E173:F173"/>
+    <mergeCell ref="E178:G178"/>
+    <mergeCell ref="E185:F185"/>
+    <mergeCell ref="E191:G191"/>
+    <mergeCell ref="E198:F198"/>
+    <mergeCell ref="E203:G203"/>
+    <mergeCell ref="E210:F210"/>
+    <mergeCell ref="E215:G215"/>
+    <mergeCell ref="E222:F222"/>
+    <mergeCell ref="E227:G227"/>
+    <mergeCell ref="E234:F234"/>
+    <mergeCell ref="E166:G166"/>
     <mergeCell ref="E145:F145"/>
     <mergeCell ref="E154:G154"/>
     <mergeCell ref="E161:F161"/>
-    <mergeCell ref="E168:G168"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E42:F42"/>
@@ -3966,6 +3961,10 @@
     <mergeCell ref="E91:G91"/>
     <mergeCell ref="E25:G25"/>
     <mergeCell ref="E98:F98"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="E138:G138"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
